--- a/data/upload/packing/TJ-25-26-182 ( Small Bore ).xlsx
+++ b/data/upload/packing/TJ-25-26-182 ( Small Bore ).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\TJ-25-26-182 NE ( Vicksburg )\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\TJ-25-26-182 NE ( Vicksburg )\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA937A89-867A-4D34-BFFD-29783E1DFA5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7745785B-46EA-4E18-A9FA-9F4610F44CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spool List ( Small Bore )" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4512" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4631" uniqueCount="1198">
   <si>
     <t>Project Code</t>
   </si>
@@ -3684,12 +3684,11 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3729,6 +3728,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9F9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3815,7 +3820,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3860,6 +3865,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4328,13 +4336,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NavDataRegion" displayName="NavDataRegion" ref="A2:Q619" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18">
-  <autoFilter ref="A2:Q619" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="4">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:Q619" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Project Code" dataDxfId="16"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Drawing No." dataDxfId="15"/>
@@ -4654,11 +4656,11 @@
       </c>
       <c r="J1" s="5">
         <f>SUBTOTAL(9,NavDataRegion[Total Qty])</f>
-        <v>162</v>
+        <v>617</v>
       </c>
       <c r="K1" s="6">
         <f>SUBTOTAL(9,NavDataRegion[Total Wt])</f>
-        <v>4799.4518900000003</v>
+        <v>16596.344509999995</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4714,7 +4716,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -4758,7 +4760,7 @@
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
     </row>
-    <row r="4" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -4802,7 +4804,7 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -4846,7 +4848,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4890,7 +4892,7 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -4934,7 +4936,7 @@
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -5030,7 +5032,7 @@
       </c>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -5044,7 +5046,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2">
+        <v>21</v>
+      </c>
       <c r="F10" s="2" t="s">
         <v>782</v>
       </c>
@@ -5072,11 +5076,15 @@
       <c r="N10" s="10">
         <v>46227</v>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
+      <c r="O10" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -5120,7 +5128,7 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -5164,7 +5172,7 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -5203,7 +5211,9 @@
       <c r="M13" s="2">
         <v>0.5</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" s="10">
+        <v>46230</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
@@ -5312,7 +5322,7 @@
       </c>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -5326,7 +5336,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2">
+        <v>21</v>
+      </c>
       <c r="F16" s="2" t="s">
         <v>1063</v>
       </c>
@@ -5354,11 +5366,15 @@
       <c r="N16" s="10">
         <v>46227</v>
       </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
+      <c r="O16" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -5402,7 +5418,7 @@
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
@@ -5446,7 +5462,7 @@
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
@@ -5542,7 +5558,7 @@
       </c>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -5556,7 +5572,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="2">
+        <v>21</v>
+      </c>
       <c r="F21" s="2" t="s">
         <v>13</v>
       </c>
@@ -5584,11 +5602,15 @@
       <c r="N21" s="10">
         <v>46227</v>
       </c>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
+      <c r="O21" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
@@ -5602,7 +5624,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="2">
+        <v>21</v>
+      </c>
       <c r="F22" s="2" t="s">
         <v>59</v>
       </c>
@@ -5630,8 +5654,12 @@
       <c r="N22" s="10">
         <v>46227</v>
       </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
+      <c r="O22" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q22" s="2"/>
     </row>
     <row r="23" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5686,7 +5714,7 @@
       </c>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -5700,7 +5728,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E24" s="2"/>
+      <c r="E24" s="2">
+        <v>21</v>
+      </c>
       <c r="F24" s="2" t="s">
         <v>74</v>
       </c>
@@ -5728,8 +5758,12 @@
       <c r="N24" s="10">
         <v>46227</v>
       </c>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
+      <c r="O24" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q24" s="2"/>
     </row>
     <row r="25" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5784,7 +5818,7 @@
       </c>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -5828,7 +5862,7 @@
       <c r="P26" s="2"/>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
@@ -5867,12 +5901,14 @@
       <c r="M27" s="2">
         <v>2</v>
       </c>
-      <c r="N27" s="2"/>
+      <c r="N27" s="10">
+        <v>46230</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
@@ -5916,7 +5952,7 @@
       <c r="P28" s="2"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -6012,7 +6048,7 @@
       </c>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
@@ -6056,7 +6092,7 @@
       <c r="P31" s="2"/>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -6100,7 +6136,7 @@
       <c r="P32" s="2"/>
       <c r="Q32" s="2"/>
     </row>
-    <row r="33" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -6196,7 +6232,7 @@
       </c>
       <c r="Q34" s="2"/>
     </row>
-    <row r="35" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
@@ -6240,7 +6276,7 @@
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
     </row>
-    <row r="36" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -6279,12 +6315,14 @@
       <c r="M36" s="2">
         <v>1</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" s="10">
+        <v>46230</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
     </row>
-    <row r="37" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
@@ -6298,7 +6336,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" s="2">
+        <v>21</v>
+      </c>
       <c r="F37" s="2" t="s">
         <v>77</v>
       </c>
@@ -6326,8 +6366,12 @@
       <c r="N37" s="10">
         <v>46227</v>
       </c>
-      <c r="O37" s="2"/>
-      <c r="P37" s="2"/>
+      <c r="O37" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q37" s="2"/>
     </row>
     <row r="38" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6382,7 +6426,7 @@
       </c>
       <c r="Q38" s="2"/>
     </row>
-    <row r="39" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>12</v>
       </c>
@@ -6396,7 +6440,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" s="2">
+        <v>21</v>
+      </c>
       <c r="F39" s="2" t="s">
         <v>80</v>
       </c>
@@ -6424,8 +6470,12 @@
       <c r="N39" s="10">
         <v>46227</v>
       </c>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
+      <c r="O39" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q39" s="2"/>
     </row>
     <row r="40" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6532,7 +6582,7 @@
       </c>
       <c r="Q41" s="2"/>
     </row>
-    <row r="42" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>12</v>
       </c>
@@ -6546,7 +6596,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E42" s="2"/>
+      <c r="E42" s="2">
+        <v>21</v>
+      </c>
       <c r="F42" s="2" t="s">
         <v>83</v>
       </c>
@@ -6574,11 +6626,15 @@
       <c r="N42" s="10">
         <v>46227</v>
       </c>
-      <c r="O42" s="2"/>
-      <c r="P42" s="2"/>
+      <c r="O42" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q42" s="2"/>
     </row>
-    <row r="43" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>12</v>
       </c>
@@ -6592,7 +6648,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E43" s="2"/>
+      <c r="E43" s="2">
+        <v>21</v>
+      </c>
       <c r="F43" s="2" t="s">
         <v>86</v>
       </c>
@@ -6620,11 +6678,15 @@
       <c r="N43" s="10">
         <v>46227</v>
       </c>
-      <c r="O43" s="2"/>
-      <c r="P43" s="2"/>
+      <c r="O43" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q43" s="2"/>
     </row>
-    <row r="44" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>12</v>
       </c>
@@ -6638,7 +6700,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" s="2">
+        <v>21</v>
+      </c>
       <c r="F44" s="2" t="s">
         <v>13</v>
       </c>
@@ -6666,11 +6730,15 @@
       <c r="N44" s="10">
         <v>46227</v>
       </c>
-      <c r="O44" s="2"/>
-      <c r="P44" s="2"/>
+      <c r="O44" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q44" s="2"/>
     </row>
-    <row r="45" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -6684,7 +6752,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" s="2">
+        <v>21</v>
+      </c>
       <c r="F45" s="2" t="s">
         <v>13</v>
       </c>
@@ -6712,8 +6782,12 @@
       <c r="N45" s="10">
         <v>46227</v>
       </c>
-      <c r="O45" s="2"/>
-      <c r="P45" s="2"/>
+      <c r="O45" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q45" s="2"/>
     </row>
     <row r="46" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6872,7 +6946,7 @@
       </c>
       <c r="Q48" s="2"/>
     </row>
-    <row r="49" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -6916,7 +6990,7 @@
       <c r="P49" s="2"/>
       <c r="Q49" s="2"/>
     </row>
-    <row r="50" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>12</v>
       </c>
@@ -7012,7 +7086,7 @@
       </c>
       <c r="Q51" s="2"/>
     </row>
-    <row r="52" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -7056,7 +7130,7 @@
       <c r="P52" s="2"/>
       <c r="Q52" s="2"/>
     </row>
-    <row r="53" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -7152,7 +7226,7 @@
       </c>
       <c r="Q54" s="2"/>
     </row>
-    <row r="55" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -7196,7 +7270,7 @@
       <c r="P55" s="2"/>
       <c r="Q55" s="2"/>
     </row>
-    <row r="56" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -7210,7 +7284,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E56" s="2"/>
+      <c r="E56" s="2">
+        <v>21</v>
+      </c>
       <c r="F56" s="2" t="s">
         <v>990</v>
       </c>
@@ -7238,11 +7314,15 @@
       <c r="N56" s="10">
         <v>46227</v>
       </c>
-      <c r="O56" s="2"/>
-      <c r="P56" s="2"/>
+      <c r="O56" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q56" s="2"/>
     </row>
-    <row r="57" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -7286,7 +7366,7 @@
       <c r="P57" s="2"/>
       <c r="Q57" s="2"/>
     </row>
-    <row r="58" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -7330,7 +7410,7 @@
       <c r="P58" s="2"/>
       <c r="Q58" s="2"/>
     </row>
-    <row r="59" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -7374,7 +7454,7 @@
       <c r="P59" s="2"/>
       <c r="Q59" s="2"/>
     </row>
-    <row r="60" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>12</v>
       </c>
@@ -7418,7 +7498,7 @@
       <c r="P60" s="2"/>
       <c r="Q60" s="2"/>
     </row>
-    <row r="61" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>12</v>
       </c>
@@ -7462,7 +7542,7 @@
       <c r="P61" s="2"/>
       <c r="Q61" s="2"/>
     </row>
-    <row r="62" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>12</v>
       </c>
@@ -7506,7 +7586,7 @@
       <c r="P62" s="2"/>
       <c r="Q62" s="2"/>
     </row>
-    <row r="63" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>12</v>
       </c>
@@ -7545,12 +7625,14 @@
       <c r="M63" s="2">
         <v>1</v>
       </c>
-      <c r="N63" s="2"/>
+      <c r="N63" s="10">
+        <v>46230</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
       <c r="Q63" s="2"/>
     </row>
-    <row r="64" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>12</v>
       </c>
@@ -7594,7 +7676,7 @@
       <c r="P64" s="2"/>
       <c r="Q64" s="2"/>
     </row>
-    <row r="65" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -7638,7 +7720,7 @@
       <c r="P65" s="2"/>
       <c r="Q65" s="2"/>
     </row>
-    <row r="66" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>12</v>
       </c>
@@ -7682,7 +7764,7 @@
       <c r="P66" s="2"/>
       <c r="Q66" s="2"/>
     </row>
-    <row r="67" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>12</v>
       </c>
@@ -7696,7 +7778,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" s="2">
+        <v>21</v>
+      </c>
       <c r="F67" s="2" t="s">
         <v>1036</v>
       </c>
@@ -7724,11 +7808,15 @@
       <c r="N67" s="10">
         <v>46227</v>
       </c>
-      <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
+      <c r="O67" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q67" s="2"/>
     </row>
-    <row r="68" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
@@ -7742,7 +7830,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" s="2">
+        <v>21</v>
+      </c>
       <c r="F68" s="2" t="s">
         <v>1070</v>
       </c>
@@ -7770,11 +7860,15 @@
       <c r="N68" s="10">
         <v>46227</v>
       </c>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
+      <c r="O68" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q68" s="2"/>
     </row>
-    <row r="69" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>12</v>
       </c>
@@ -7818,7 +7912,7 @@
       <c r="P69" s="2"/>
       <c r="Q69" s="2"/>
     </row>
-    <row r="70" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>12</v>
       </c>
@@ -7862,7 +7956,7 @@
       <c r="P70" s="2"/>
       <c r="Q70" s="2"/>
     </row>
-    <row r="71" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -7876,7 +7970,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E71" s="2"/>
+      <c r="E71" s="2">
+        <v>21</v>
+      </c>
       <c r="F71" s="2" t="s">
         <v>1105</v>
       </c>
@@ -7904,11 +8000,15 @@
       <c r="N71" s="10">
         <v>46227</v>
       </c>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
+      <c r="O71" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q71" s="2"/>
     </row>
-    <row r="72" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>12</v>
       </c>
@@ -7922,7 +8022,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" s="2">
+        <v>21</v>
+      </c>
       <c r="F72" s="2" t="s">
         <v>130</v>
       </c>
@@ -7950,8 +8052,12 @@
       <c r="N72" s="10">
         <v>46227</v>
       </c>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
+      <c r="O72" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q72" s="2"/>
     </row>
     <row r="73" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8006,7 +8112,7 @@
       </c>
       <c r="Q73" s="2"/>
     </row>
-    <row r="74" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>12</v>
       </c>
@@ -8020,7 +8126,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" s="2">
+        <v>21</v>
+      </c>
       <c r="F74" s="2" t="s">
         <v>141</v>
       </c>
@@ -8048,11 +8156,15 @@
       <c r="N74" s="10">
         <v>46227</v>
       </c>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
+      <c r="O74" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q74" s="2"/>
     </row>
-    <row r="75" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>12</v>
       </c>
@@ -8096,23 +8208,25 @@
       <c r="P75" s="2"/>
       <c r="Q75" s="2"/>
     </row>
-    <row r="76" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>226</v>
+        <v>152</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>227</v>
+        <v>927</v>
       </c>
       <c r="D76" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" s="2">
+        <v>21</v>
+      </c>
       <c r="F76" s="2" t="s">
-        <v>228</v>
+        <v>928</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>24</v>
@@ -8127,20 +8241,26 @@
         <v>1</v>
       </c>
       <c r="K76" s="11">
-        <v>62.695320000000002</v>
+        <v>11.249700000000001</v>
       </c>
       <c r="L76" s="2">
-        <v>16</v>
+        <v>4.5</v>
       </c>
       <c r="M76" s="2">
-        <v>2</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="N76" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O76" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q76" s="2"/>
     </row>
-    <row r="77" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>12</v>
       </c>
@@ -8184,7 +8304,7 @@
       <c r="P77" s="2"/>
       <c r="Q77" s="2"/>
     </row>
-    <row r="78" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>12</v>
       </c>
@@ -8198,7 +8318,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" s="2">
+        <v>21</v>
+      </c>
       <c r="F78" s="2" t="s">
         <v>127</v>
       </c>
@@ -8226,8 +8348,12 @@
       <c r="N78" s="10">
         <v>46227</v>
       </c>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
+      <c r="O78" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q78" s="2"/>
     </row>
     <row r="79" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8282,7 +8408,7 @@
       </c>
       <c r="Q79" s="2"/>
     </row>
-    <row r="80" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>12</v>
       </c>
@@ -8326,7 +8452,7 @@
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
     </row>
-    <row r="81" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -8370,7 +8496,7 @@
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
     </row>
-    <row r="82" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>12</v>
       </c>
@@ -8414,23 +8540,25 @@
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
     </row>
-    <row r="83" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>245</v>
+        <v>1081</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>246</v>
+        <v>1082</v>
       </c>
       <c r="D83" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E83" s="2"/>
+      <c r="E83" s="2">
+        <v>21</v>
+      </c>
       <c r="F83" s="2" t="s">
-        <v>247</v>
+        <v>1083</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>24</v>
@@ -8439,42 +8567,50 @@
         <v>14</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" s="2">
         <v>1</v>
       </c>
       <c r="K83" s="11">
-        <v>9.8984400000000008</v>
+        <v>4.2122000000000002</v>
       </c>
       <c r="L83" s="2">
-        <v>9</v>
+        <v>2.25</v>
       </c>
       <c r="M83" s="2">
-        <v>1</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="N83" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O83" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q83" s="2"/>
     </row>
-    <row r="84" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>248</v>
+        <v>1072</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>249</v>
+        <v>1124</v>
       </c>
       <c r="D84" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E84" s="2"/>
+      <c r="E84" s="2">
+        <v>21</v>
+      </c>
       <c r="F84" s="2" t="s">
-        <v>250</v>
+        <v>1125</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>24</v>
@@ -8489,20 +8625,26 @@
         <v>1</v>
       </c>
       <c r="K84" s="11">
-        <v>10.44354</v>
+        <v>10.2316</v>
       </c>
       <c r="L84" s="2">
-        <v>10</v>
+        <v>6.75</v>
       </c>
       <c r="M84" s="2">
-        <v>1</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="N84" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O84" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q84" s="2"/>
     </row>
-    <row r="85" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>12</v>
       </c>
@@ -8546,7 +8688,7 @@
       <c r="P85" s="2"/>
       <c r="Q85" s="2"/>
     </row>
-    <row r="86" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>12</v>
       </c>
@@ -8590,7 +8732,7 @@
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
     </row>
-    <row r="87" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>12</v>
       </c>
@@ -8634,23 +8776,25 @@
       <c r="P87" s="2"/>
       <c r="Q87" s="2"/>
     </row>
-    <row r="88" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>260</v>
+        <v>1136</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>261</v>
+        <v>1137</v>
       </c>
       <c r="D88" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" s="2">
+        <v>21</v>
+      </c>
       <c r="F88" s="2" t="s">
-        <v>262</v>
+        <v>1138</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>24</v>
@@ -8659,23 +8803,29 @@
         <v>14</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J88" s="2">
         <v>1</v>
       </c>
       <c r="K88" s="11">
-        <v>9.5525400000000005</v>
+        <v>4.4652000000000003</v>
       </c>
       <c r="L88" s="2">
-        <v>10</v>
+        <v>2.25</v>
       </c>
       <c r="M88" s="2">
-        <v>1</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="N88" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O88" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q88" s="2"/>
     </row>
     <row r="89" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8730,7 +8880,7 @@
       </c>
       <c r="Q89" s="2"/>
     </row>
-    <row r="90" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>12</v>
       </c>
@@ -8826,7 +8976,7 @@
       </c>
       <c r="Q91" s="2"/>
     </row>
-    <row r="92" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>12</v>
       </c>
@@ -8870,7 +9020,7 @@
       <c r="P92" s="2"/>
       <c r="Q92" s="2"/>
     </row>
-    <row r="93" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>12</v>
       </c>
@@ -8884,7 +9034,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E93" s="2"/>
+      <c r="E93" s="2">
+        <v>21</v>
+      </c>
       <c r="F93" s="2" t="s">
         <v>127</v>
       </c>
@@ -8912,8 +9064,12 @@
       <c r="N93" s="10">
         <v>46227</v>
       </c>
-      <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
+      <c r="O93" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q93" s="2"/>
     </row>
     <row r="94" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8968,7 +9124,7 @@
       </c>
       <c r="Q94" s="2"/>
     </row>
-    <row r="95" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>12</v>
       </c>
@@ -9012,7 +9168,7 @@
       <c r="P95" s="2"/>
       <c r="Q95" s="2"/>
     </row>
-    <row r="96" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>12</v>
       </c>
@@ -9056,23 +9212,25 @@
       <c r="P96" s="2"/>
       <c r="Q96" s="2"/>
     </row>
-    <row r="97" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
       <c r="D97" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E97" s="2"/>
+      <c r="E97" s="2">
+        <v>21</v>
+      </c>
       <c r="F97" s="2" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>24</v>
@@ -9087,36 +9245,44 @@
         <v>1</v>
       </c>
       <c r="K97" s="11">
-        <v>14.2242</v>
+        <v>9.8984400000000008</v>
       </c>
       <c r="L97" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M97" s="2">
         <v>1</v>
       </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" s="2"/>
+      <c r="N97" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O97" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q97" s="2"/>
     </row>
-    <row r="98" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="D98" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E98" s="2"/>
+      <c r="E98" s="2">
+        <v>21</v>
+      </c>
       <c r="F98" s="2" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>24</v>
@@ -9131,20 +9297,26 @@
         <v>1</v>
       </c>
       <c r="K98" s="11">
-        <v>14.2242</v>
+        <v>10.44354</v>
       </c>
       <c r="L98" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M98" s="2">
         <v>1</v>
       </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" s="2"/>
+      <c r="N98" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O98" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q98" s="2"/>
     </row>
-    <row r="99" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>12</v>
       </c>
@@ -9188,7 +9360,7 @@
       <c r="P99" s="2"/>
       <c r="Q99" s="2"/>
     </row>
-    <row r="100" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>12</v>
       </c>
@@ -9232,7 +9404,7 @@
       <c r="P100" s="2"/>
       <c r="Q100" s="2"/>
     </row>
-    <row r="101" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>12</v>
       </c>
@@ -9276,7 +9448,7 @@
       <c r="P101" s="2"/>
       <c r="Q101" s="2"/>
     </row>
-    <row r="102" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>12</v>
       </c>
@@ -9320,7 +9492,7 @@
       <c r="P102" s="2"/>
       <c r="Q102" s="2"/>
     </row>
-    <row r="103" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>12</v>
       </c>
@@ -9364,23 +9536,25 @@
       <c r="P103" s="2"/>
       <c r="Q103" s="2"/>
     </row>
-    <row r="104" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>306</v>
+        <v>261</v>
       </c>
       <c r="D104" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E104" s="2"/>
+      <c r="E104" s="2">
+        <v>21</v>
+      </c>
       <c r="F104" s="2" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>24</v>
@@ -9389,23 +9563,29 @@
         <v>14</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J104" s="2">
         <v>1</v>
       </c>
       <c r="K104" s="11">
-        <v>10.317959999999999</v>
+        <v>9.5525400000000005</v>
       </c>
       <c r="L104" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M104" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="N104" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O104" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q104" s="2"/>
     </row>
     <row r="105" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9460,7 +9640,7 @@
       </c>
       <c r="Q105" s="2"/>
     </row>
-    <row r="106" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>12</v>
       </c>
@@ -9504,7 +9684,7 @@
       <c r="P106" s="2"/>
       <c r="Q106" s="2"/>
     </row>
-    <row r="107" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>12</v>
       </c>
@@ -9518,7 +9698,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E107" s="2"/>
+      <c r="E107" s="2">
+        <v>21</v>
+      </c>
       <c r="F107" s="2" t="s">
         <v>127</v>
       </c>
@@ -9546,11 +9728,15 @@
       <c r="N107" s="10">
         <v>46227</v>
       </c>
-      <c r="O107" s="2"/>
-      <c r="P107" s="2"/>
+      <c r="O107" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P107" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q107" s="2"/>
     </row>
-    <row r="108" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>12</v>
       </c>
@@ -9564,7 +9750,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" s="2">
+        <v>21</v>
+      </c>
       <c r="F108" s="2" t="s">
         <v>146</v>
       </c>
@@ -9592,11 +9780,15 @@
       <c r="N108" s="10">
         <v>46227</v>
       </c>
-      <c r="O108" s="2"/>
-      <c r="P108" s="2"/>
+      <c r="O108" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q108" s="2"/>
     </row>
-    <row r="109" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>12</v>
       </c>
@@ -9640,7 +9832,7 @@
       <c r="P109" s="2"/>
       <c r="Q109" s="2"/>
     </row>
-    <row r="110" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>12</v>
       </c>
@@ -9684,7 +9876,7 @@
       <c r="P110" s="2"/>
       <c r="Q110" s="2"/>
     </row>
-    <row r="111" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>12</v>
       </c>
@@ -9728,7 +9920,7 @@
       <c r="P111" s="2"/>
       <c r="Q111" s="2"/>
     </row>
-    <row r="112" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>12</v>
       </c>
@@ -9772,7 +9964,7 @@
       <c r="P112" s="2"/>
       <c r="Q112" s="2"/>
     </row>
-    <row r="113" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -9816,7 +10008,7 @@
       <c r="P113" s="2"/>
       <c r="Q113" s="2"/>
     </row>
-    <row r="114" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>12</v>
       </c>
@@ -9860,7 +10052,7 @@
       <c r="P114" s="2"/>
       <c r="Q114" s="2"/>
     </row>
-    <row r="115" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>12</v>
       </c>
@@ -9904,7 +10096,7 @@
       <c r="P115" s="2"/>
       <c r="Q115" s="2"/>
     </row>
-    <row r="116" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>12</v>
       </c>
@@ -9918,7 +10110,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E116" s="2"/>
+      <c r="E116" s="2">
+        <v>21</v>
+      </c>
       <c r="F116" s="2" t="s">
         <v>13</v>
       </c>
@@ -9946,11 +10140,15 @@
       <c r="N116" s="10">
         <v>46227</v>
       </c>
-      <c r="O116" s="2"/>
-      <c r="P116" s="2"/>
+      <c r="O116" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q116" s="2"/>
     </row>
-    <row r="117" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>12</v>
       </c>
@@ -9994,7 +10192,7 @@
       <c r="P117" s="2"/>
       <c r="Q117" s="2"/>
     </row>
-    <row r="118" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>12</v>
       </c>
@@ -10142,7 +10340,7 @@
       </c>
       <c r="Q120" s="2"/>
     </row>
-    <row r="121" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>12</v>
       </c>
@@ -10156,7 +10354,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E121" s="2"/>
+      <c r="E121" s="2">
+        <v>21</v>
+      </c>
       <c r="F121" s="2" t="s">
         <v>151</v>
       </c>
@@ -10184,11 +10384,15 @@
       <c r="N121" s="10">
         <v>46227</v>
       </c>
-      <c r="O121" s="2"/>
-      <c r="P121" s="2"/>
+      <c r="O121" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P121" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q121" s="2"/>
     </row>
-    <row r="122" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>12</v>
       </c>
@@ -10232,7 +10436,7 @@
       <c r="P122" s="2"/>
       <c r="Q122" s="2"/>
     </row>
-    <row r="123" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>12</v>
       </c>
@@ -10276,7 +10480,7 @@
       <c r="P123" s="2"/>
       <c r="Q123" s="2"/>
     </row>
-    <row r="124" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>12</v>
       </c>
@@ -10320,7 +10524,7 @@
       <c r="P124" s="2"/>
       <c r="Q124" s="2"/>
     </row>
-    <row r="125" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>12</v>
       </c>
@@ -10364,7 +10568,7 @@
       <c r="P125" s="2"/>
       <c r="Q125" s="2"/>
     </row>
-    <row r="126" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>12</v>
       </c>
@@ -10408,7 +10612,7 @@
       <c r="P126" s="2"/>
       <c r="Q126" s="2"/>
     </row>
-    <row r="127" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>12</v>
       </c>
@@ -10452,7 +10656,7 @@
       <c r="P127" s="2"/>
       <c r="Q127" s="2"/>
     </row>
-    <row r="128" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>12</v>
       </c>
@@ -10496,7 +10700,7 @@
       <c r="P128" s="2"/>
       <c r="Q128" s="2"/>
     </row>
-    <row r="129" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>12</v>
       </c>
@@ -10540,7 +10744,7 @@
       <c r="P129" s="2"/>
       <c r="Q129" s="2"/>
     </row>
-    <row r="130" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>12</v>
       </c>
@@ -10584,7 +10788,7 @@
       <c r="P130" s="2"/>
       <c r="Q130" s="2"/>
     </row>
-    <row r="131" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>12</v>
       </c>
@@ -10628,7 +10832,7 @@
       <c r="P131" s="2"/>
       <c r="Q131" s="2"/>
     </row>
-    <row r="132" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>12</v>
       </c>
@@ -10672,7 +10876,7 @@
       <c r="P132" s="2"/>
       <c r="Q132" s="2"/>
     </row>
-    <row r="133" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>12</v>
       </c>
@@ -10716,7 +10920,7 @@
       <c r="P133" s="2"/>
       <c r="Q133" s="2"/>
     </row>
-    <row r="134" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>12</v>
       </c>
@@ -10760,7 +10964,7 @@
       <c r="P134" s="2"/>
       <c r="Q134" s="2"/>
     </row>
-    <row r="135" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>12</v>
       </c>
@@ -10856,7 +11060,7 @@
       </c>
       <c r="Q136" s="2"/>
     </row>
-    <row r="137" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>12</v>
       </c>
@@ -10900,23 +11104,25 @@
       <c r="P137" s="2"/>
       <c r="Q137" s="2"/>
     </row>
-    <row r="138" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>400</v>
+        <v>286</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>401</v>
+        <v>287</v>
       </c>
       <c r="D138" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E138" s="2"/>
+      <c r="E138" s="2">
+        <v>21</v>
+      </c>
       <c r="F138" s="2" t="s">
-        <v>402</v>
+        <v>288</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>24</v>
@@ -10931,20 +11137,26 @@
         <v>1</v>
       </c>
       <c r="K138" s="11">
-        <v>11.96556</v>
+        <v>14.2242</v>
       </c>
       <c r="L138" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M138" s="2">
         <v>1</v>
       </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" s="2"/>
+      <c r="N138" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O138" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P138" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q138" s="2"/>
     </row>
-    <row r="139" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>12</v>
       </c>
@@ -10988,7 +11200,7 @@
       <c r="P139" s="2"/>
       <c r="Q139" s="2"/>
     </row>
-    <row r="140" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>12</v>
       </c>
@@ -11032,7 +11244,7 @@
       <c r="P140" s="2"/>
       <c r="Q140" s="2"/>
     </row>
-    <row r="141" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>12</v>
       </c>
@@ -11076,7 +11288,7 @@
       <c r="P141" s="2"/>
       <c r="Q141" s="2"/>
     </row>
-    <row r="142" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>12</v>
       </c>
@@ -11120,7 +11332,7 @@
       <c r="P142" s="2"/>
       <c r="Q142" s="2"/>
     </row>
-    <row r="143" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>12</v>
       </c>
@@ -11164,7 +11376,7 @@
       <c r="P143" s="2"/>
       <c r="Q143" s="2"/>
     </row>
-    <row r="144" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>12</v>
       </c>
@@ -11208,7 +11420,7 @@
       <c r="P144" s="2"/>
       <c r="Q144" s="2"/>
     </row>
-    <row r="145" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>12</v>
       </c>
@@ -11252,23 +11464,25 @@
       <c r="P145" s="2"/>
       <c r="Q145" s="2"/>
     </row>
-    <row r="146" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>422</v>
+        <v>289</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>423</v>
+        <v>290</v>
       </c>
       <c r="D146" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E146" s="2"/>
+      <c r="E146" s="2">
+        <v>21</v>
+      </c>
       <c r="F146" s="2" t="s">
-        <v>424</v>
+        <v>291</v>
       </c>
       <c r="G146" s="2" t="s">
         <v>24</v>
@@ -11283,20 +11497,26 @@
         <v>1</v>
       </c>
       <c r="K146" s="11">
-        <v>18.102319999999999</v>
+        <v>14.2242</v>
       </c>
       <c r="L146" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M146" s="2">
         <v>1</v>
       </c>
-      <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
-      <c r="P146" s="2"/>
+      <c r="N146" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O146" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P146" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q146" s="2"/>
     </row>
-    <row r="147" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>12</v>
       </c>
@@ -11340,7 +11560,7 @@
       <c r="P147" s="2"/>
       <c r="Q147" s="2"/>
     </row>
-    <row r="148" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>12</v>
       </c>
@@ -11384,7 +11604,7 @@
       <c r="P148" s="2"/>
       <c r="Q148" s="2"/>
     </row>
-    <row r="149" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>12</v>
       </c>
@@ -11428,7 +11648,7 @@
       <c r="P149" s="2"/>
       <c r="Q149" s="2"/>
     </row>
-    <row r="150" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>12</v>
       </c>
@@ -11472,7 +11692,7 @@
       <c r="P150" s="2"/>
       <c r="Q150" s="2"/>
     </row>
-    <row r="151" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>12</v>
       </c>
@@ -11516,7 +11736,7 @@
       <c r="P151" s="2"/>
       <c r="Q151" s="2"/>
     </row>
-    <row r="152" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>12</v>
       </c>
@@ -11530,7 +11750,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E152" s="2"/>
+      <c r="E152" s="2">
+        <v>21</v>
+      </c>
       <c r="F152" s="2" t="s">
         <v>1108</v>
       </c>
@@ -11558,8 +11780,12 @@
       <c r="N152" s="10">
         <v>46227</v>
       </c>
-      <c r="O152" s="2"/>
-      <c r="P152" s="2"/>
+      <c r="O152" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P152" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q152" s="2"/>
     </row>
     <row r="153" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11666,7 +11892,7 @@
       </c>
       <c r="Q154" s="2"/>
     </row>
-    <row r="155" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>12</v>
       </c>
@@ -11710,7 +11936,7 @@
       <c r="P155" s="2"/>
       <c r="Q155" s="2"/>
     </row>
-    <row r="156" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>12</v>
       </c>
@@ -11724,7 +11950,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E156" s="2"/>
+      <c r="E156" s="2">
+        <v>21</v>
+      </c>
       <c r="F156" s="2" t="s">
         <v>997</v>
       </c>
@@ -11752,11 +11980,15 @@
       <c r="N156" s="10">
         <v>46227</v>
       </c>
-      <c r="O156" s="2"/>
-      <c r="P156" s="2"/>
+      <c r="O156" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P156" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q156" s="2"/>
     </row>
-    <row r="157" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>12</v>
       </c>
@@ -11800,7 +12032,7 @@
       <c r="P157" s="2"/>
       <c r="Q157" s="2"/>
     </row>
-    <row r="158" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>12</v>
       </c>
@@ -11844,7 +12076,7 @@
       <c r="P158" s="2"/>
       <c r="Q158" s="2"/>
     </row>
-    <row r="159" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>12</v>
       </c>
@@ -11888,7 +12120,7 @@
       <c r="P159" s="2"/>
       <c r="Q159" s="2"/>
     </row>
-    <row r="160" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>12</v>
       </c>
@@ -11984,7 +12216,7 @@
       </c>
       <c r="Q161" s="2"/>
     </row>
-    <row r="162" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>12</v>
       </c>
@@ -12028,7 +12260,7 @@
       <c r="P162" s="2"/>
       <c r="Q162" s="2"/>
     </row>
-    <row r="163" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>12</v>
       </c>
@@ -12124,7 +12356,7 @@
       </c>
       <c r="Q164" s="2"/>
     </row>
-    <row r="165" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>12</v>
       </c>
@@ -12168,7 +12400,7 @@
       <c r="P165" s="2"/>
       <c r="Q165" s="2"/>
     </row>
-    <row r="166" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>12</v>
       </c>
@@ -12212,7 +12444,7 @@
       <c r="P166" s="2"/>
       <c r="Q166" s="2"/>
     </row>
-    <row r="167" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>12</v>
       </c>
@@ -12308,23 +12540,25 @@
       </c>
       <c r="Q168" s="2"/>
     </row>
-    <row r="169" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>488</v>
+        <v>400</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>489</v>
+        <v>401</v>
       </c>
       <c r="D169" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E169" s="2"/>
+      <c r="E169" s="2">
+        <v>21</v>
+      </c>
       <c r="F169" s="2" t="s">
-        <v>13</v>
+        <v>402</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>24</v>
@@ -12339,20 +12573,26 @@
         <v>1</v>
       </c>
       <c r="K169" s="11">
-        <v>3.1048399999999998</v>
+        <v>11.96556</v>
       </c>
       <c r="L169" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M169" s="2">
         <v>1</v>
       </c>
-      <c r="N169" s="2"/>
-      <c r="O169" s="2"/>
-      <c r="P169" s="2"/>
+      <c r="N169" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O169" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P169" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q169" s="2"/>
     </row>
-    <row r="170" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>12</v>
       </c>
@@ -12396,7 +12636,7 @@
       <c r="P170" s="2"/>
       <c r="Q170" s="2"/>
     </row>
-    <row r="171" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>12</v>
       </c>
@@ -12440,7 +12680,7 @@
       <c r="P171" s="2"/>
       <c r="Q171" s="2"/>
     </row>
-    <row r="172" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>12</v>
       </c>
@@ -12484,7 +12724,7 @@
       <c r="P172" s="2"/>
       <c r="Q172" s="2"/>
     </row>
-    <row r="173" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>12</v>
       </c>
@@ -12528,7 +12768,7 @@
       <c r="P173" s="2"/>
       <c r="Q173" s="2"/>
     </row>
-    <row r="174" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>12</v>
       </c>
@@ -12542,7 +12782,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E174" s="2"/>
+      <c r="E174" s="2">
+        <v>21</v>
+      </c>
       <c r="F174" s="2" t="s">
         <v>829</v>
       </c>
@@ -12570,11 +12812,15 @@
       <c r="N174" s="10">
         <v>46227</v>
       </c>
-      <c r="O174" s="2"/>
-      <c r="P174" s="2"/>
+      <c r="O174" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P174" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q174" s="2"/>
     </row>
-    <row r="175" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>12</v>
       </c>
@@ -12588,7 +12834,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E175" s="2"/>
+      <c r="E175" s="2">
+        <v>21</v>
+      </c>
       <c r="F175" s="2" t="s">
         <v>935</v>
       </c>
@@ -12616,11 +12864,15 @@
       <c r="N175" s="10">
         <v>46227</v>
       </c>
-      <c r="O175" s="2"/>
-      <c r="P175" s="2"/>
+      <c r="O175" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P175" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q175" s="2"/>
     </row>
-    <row r="176" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>12</v>
       </c>
@@ -12664,7 +12916,7 @@
       <c r="P176" s="2"/>
       <c r="Q176" s="2"/>
     </row>
-    <row r="177" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>12</v>
       </c>
@@ -12708,7 +12960,7 @@
       <c r="P177" s="2"/>
       <c r="Q177" s="2"/>
     </row>
-    <row r="178" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>12</v>
       </c>
@@ -12722,7 +12974,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E178" s="2"/>
+      <c r="E178" s="2">
+        <v>21</v>
+      </c>
       <c r="F178" s="2" t="s">
         <v>999</v>
       </c>
@@ -12750,11 +13004,15 @@
       <c r="N178" s="10">
         <v>46227</v>
       </c>
-      <c r="O178" s="2"/>
-      <c r="P178" s="2"/>
+      <c r="O178" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P178" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q178" s="2"/>
     </row>
-    <row r="179" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>12</v>
       </c>
@@ -12768,7 +13026,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E179" s="2"/>
+      <c r="E179" s="2">
+        <v>21</v>
+      </c>
       <c r="F179" s="2" t="s">
         <v>1040</v>
       </c>
@@ -12796,11 +13056,15 @@
       <c r="N179" s="10">
         <v>46227</v>
       </c>
-      <c r="O179" s="2"/>
-      <c r="P179" s="2"/>
+      <c r="O179" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P179" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q179" s="2"/>
     </row>
-    <row r="180" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>12</v>
       </c>
@@ -12814,7 +13078,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E180" s="2"/>
+      <c r="E180" s="2">
+        <v>21</v>
+      </c>
       <c r="F180" s="2" t="s">
         <v>1077</v>
       </c>
@@ -12842,11 +13108,15 @@
       <c r="N180" s="10">
         <v>46227</v>
       </c>
-      <c r="O180" s="2"/>
-      <c r="P180" s="2"/>
+      <c r="O180" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P180" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q180" s="2"/>
     </row>
-    <row r="181" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>12</v>
       </c>
@@ -12890,7 +13160,7 @@
       <c r="P181" s="2"/>
       <c r="Q181" s="2"/>
     </row>
-    <row r="182" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>12</v>
       </c>
@@ -12934,7 +13204,7 @@
       <c r="P182" s="2"/>
       <c r="Q182" s="2"/>
     </row>
-    <row r="183" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>12</v>
       </c>
@@ -12978,7 +13248,7 @@
       <c r="P183" s="2"/>
       <c r="Q183" s="2"/>
     </row>
-    <row r="184" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>12</v>
       </c>
@@ -13022,7 +13292,7 @@
       <c r="P184" s="2"/>
       <c r="Q184" s="2"/>
     </row>
-    <row r="185" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>12</v>
       </c>
@@ -13036,7 +13306,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E185" s="2"/>
+      <c r="E185" s="2">
+        <v>21</v>
+      </c>
       <c r="F185" s="2" t="s">
         <v>1111</v>
       </c>
@@ -13064,27 +13336,33 @@
       <c r="N185" s="10">
         <v>46227</v>
       </c>
-      <c r="O185" s="2"/>
-      <c r="P185" s="2"/>
+      <c r="O185" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P185" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q185" s="2"/>
     </row>
-    <row r="186" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>530</v>
+        <v>422</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>531</v>
+        <v>423</v>
       </c>
       <c r="D186" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E186" s="2"/>
+      <c r="E186" s="2">
+        <v>21</v>
+      </c>
       <c r="F186" s="2" t="s">
-        <v>532</v>
+        <v>424</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>24</v>
@@ -13099,34 +13377,42 @@
         <v>1</v>
       </c>
       <c r="K186" s="11">
-        <v>12.6402</v>
+        <v>18.102319999999999</v>
       </c>
       <c r="L186" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M186" s="2">
         <v>1</v>
       </c>
-      <c r="N186" s="2"/>
-      <c r="O186" s="2"/>
-      <c r="P186" s="2"/>
+      <c r="N186" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O186" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P186" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q186" s="2"/>
     </row>
-    <row r="187" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>533</v>
+        <v>488</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>534</v>
+        <v>489</v>
       </c>
       <c r="D187" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E187" s="2"/>
+      <c r="E187" s="2">
+        <v>21</v>
+      </c>
       <c r="F187" s="2" t="s">
         <v>13</v>
       </c>
@@ -13143,20 +13429,26 @@
         <v>1</v>
       </c>
       <c r="K187" s="11">
-        <v>17.058309999999999</v>
+        <v>3.1048399999999998</v>
       </c>
       <c r="L187" s="2">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="M187" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
-      <c r="P187" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="N187" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O187" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P187" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q187" s="2"/>
     </row>
-    <row r="188" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>12</v>
       </c>
@@ -13200,7 +13492,7 @@
       <c r="P188" s="2"/>
       <c r="Q188" s="2"/>
     </row>
-    <row r="189" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>12</v>
       </c>
@@ -13244,7 +13536,7 @@
       <c r="P189" s="2"/>
       <c r="Q189" s="2"/>
     </row>
-    <row r="190" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>12</v>
       </c>
@@ -13288,7 +13580,7 @@
       <c r="P190" s="2"/>
       <c r="Q190" s="2"/>
     </row>
-    <row r="191" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>12</v>
       </c>
@@ -13332,7 +13624,7 @@
       <c r="P191" s="2"/>
       <c r="Q191" s="2"/>
     </row>
-    <row r="192" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>12</v>
       </c>
@@ -13376,7 +13668,7 @@
       <c r="P192" s="2"/>
       <c r="Q192" s="2"/>
     </row>
-    <row r="193" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>12</v>
       </c>
@@ -13420,7 +13712,7 @@
       <c r="P193" s="2"/>
       <c r="Q193" s="2"/>
     </row>
-    <row r="194" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>12</v>
       </c>
@@ -13464,7 +13756,7 @@
       <c r="P194" s="2"/>
       <c r="Q194" s="2"/>
     </row>
-    <row r="195" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>12</v>
       </c>
@@ -13478,7 +13770,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E195" s="2"/>
+      <c r="E195" s="2">
+        <v>21</v>
+      </c>
       <c r="F195" s="2" t="s">
         <v>1128</v>
       </c>
@@ -13506,11 +13800,15 @@
       <c r="N195" s="10">
         <v>46227</v>
       </c>
-      <c r="O195" s="2"/>
-      <c r="P195" s="2"/>
+      <c r="O195" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P195" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q195" s="2"/>
     </row>
-    <row r="196" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>12</v>
       </c>
@@ -13554,7 +13852,7 @@
       <c r="P196" s="2"/>
       <c r="Q196" s="2"/>
     </row>
-    <row r="197" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>12</v>
       </c>
@@ -13650,7 +13948,7 @@
       </c>
       <c r="Q198" s="2"/>
     </row>
-    <row r="199" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>12</v>
       </c>
@@ -13694,7 +13992,7 @@
       <c r="P199" s="2"/>
       <c r="Q199" s="2"/>
     </row>
-    <row r="200" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>12</v>
       </c>
@@ -13738,7 +14036,7 @@
       <c r="P200" s="2"/>
       <c r="Q200" s="2"/>
     </row>
-    <row r="201" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>12</v>
       </c>
@@ -13782,7 +14080,7 @@
       <c r="P201" s="2"/>
       <c r="Q201" s="2"/>
     </row>
-    <row r="202" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>12</v>
       </c>
@@ -13826,7 +14124,7 @@
       <c r="P202" s="2"/>
       <c r="Q202" s="2"/>
     </row>
-    <row r="203" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>12</v>
       </c>
@@ -13870,7 +14168,7 @@
       <c r="P203" s="2"/>
       <c r="Q203" s="2"/>
     </row>
-    <row r="204" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>12</v>
       </c>
@@ -13914,7 +14212,7 @@
       <c r="P204" s="2"/>
       <c r="Q204" s="2"/>
     </row>
-    <row r="205" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>12</v>
       </c>
@@ -13958,7 +14256,7 @@
       <c r="P205" s="2"/>
       <c r="Q205" s="2"/>
     </row>
-    <row r="206" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>12</v>
       </c>
@@ -14002,23 +14300,25 @@
       <c r="P206" s="2"/>
       <c r="Q206" s="2"/>
     </row>
-    <row r="207" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>575</v>
+        <v>530</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>576</v>
+        <v>531</v>
       </c>
       <c r="D207" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E207" s="2"/>
+      <c r="E207" s="2">
+        <v>21</v>
+      </c>
       <c r="F207" s="2" t="s">
-        <v>13</v>
+        <v>532</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>24</v>
@@ -14027,13 +14327,13 @@
         <v>14</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J207" s="2">
         <v>1</v>
       </c>
       <c r="K207" s="11">
-        <v>10.677759999999999</v>
+        <v>12.6402</v>
       </c>
       <c r="L207" s="2">
         <v>9</v>
@@ -14041,12 +14341,18 @@
       <c r="M207" s="2">
         <v>1</v>
       </c>
-      <c r="N207" s="2"/>
-      <c r="O207" s="2"/>
-      <c r="P207" s="2"/>
+      <c r="N207" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O207" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P207" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q207" s="2"/>
     </row>
-    <row r="208" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>12</v>
       </c>
@@ -14090,7 +14396,7 @@
       <c r="P208" s="2"/>
       <c r="Q208" s="2"/>
     </row>
-    <row r="209" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>12</v>
       </c>
@@ -14134,7 +14440,7 @@
       <c r="P209" s="2"/>
       <c r="Q209" s="2"/>
     </row>
-    <row r="210" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>12</v>
       </c>
@@ -14178,7 +14484,7 @@
       <c r="P210" s="2"/>
       <c r="Q210" s="2"/>
     </row>
-    <row r="211" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>12</v>
       </c>
@@ -14222,7 +14528,7 @@
       <c r="P211" s="2"/>
       <c r="Q211" s="2"/>
     </row>
-    <row r="212" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>12</v>
       </c>
@@ -14266,7 +14572,7 @@
       <c r="P212" s="2"/>
       <c r="Q212" s="2"/>
     </row>
-    <row r="213" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>12</v>
       </c>
@@ -14310,7 +14616,7 @@
       <c r="P213" s="2"/>
       <c r="Q213" s="2"/>
     </row>
-    <row r="214" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>12</v>
       </c>
@@ -14354,7 +14660,7 @@
       <c r="P214" s="2"/>
       <c r="Q214" s="2"/>
     </row>
-    <row r="215" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>12</v>
       </c>
@@ -14398,7 +14704,7 @@
       <c r="P215" s="2"/>
       <c r="Q215" s="2"/>
     </row>
-    <row r="216" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>12</v>
       </c>
@@ -14437,7 +14743,9 @@
       <c r="M216" s="2">
         <v>0.5</v>
       </c>
-      <c r="N216" s="2"/>
+      <c r="N216" s="10">
+        <v>46230</v>
+      </c>
       <c r="O216" s="2"/>
       <c r="P216" s="2"/>
       <c r="Q216" s="2"/>
@@ -14702,7 +15010,7 @@
       </c>
       <c r="Q221" s="2"/>
     </row>
-    <row r="222" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>12</v>
       </c>
@@ -14746,7 +15054,7 @@
       <c r="P222" s="2"/>
       <c r="Q222" s="2"/>
     </row>
-    <row r="223" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>12</v>
       </c>
@@ -14790,7 +15098,7 @@
       <c r="P223" s="2"/>
       <c r="Q223" s="2"/>
     </row>
-    <row r="224" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>12</v>
       </c>
@@ -14886,7 +15194,7 @@
       </c>
       <c r="Q225" s="2"/>
     </row>
-    <row r="226" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>12</v>
       </c>
@@ -14982,7 +15290,7 @@
       </c>
       <c r="Q227" s="2"/>
     </row>
-    <row r="228" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>12</v>
       </c>
@@ -15026,7 +15334,7 @@
       <c r="P228" s="2"/>
       <c r="Q228" s="2"/>
     </row>
-    <row r="229" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>12</v>
       </c>
@@ -15070,7 +15378,7 @@
       <c r="P229" s="2"/>
       <c r="Q229" s="2"/>
     </row>
-    <row r="230" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>12</v>
       </c>
@@ -15270,7 +15578,7 @@
       </c>
       <c r="Q233" s="2"/>
     </row>
-    <row r="234" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>12</v>
       </c>
@@ -15314,7 +15622,7 @@
       <c r="P234" s="2"/>
       <c r="Q234" s="2"/>
     </row>
-    <row r="235" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>12</v>
       </c>
@@ -15358,7 +15666,7 @@
       <c r="P235" s="2"/>
       <c r="Q235" s="2"/>
     </row>
-    <row r="236" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>12</v>
       </c>
@@ -15372,7 +15680,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E236" s="2"/>
+      <c r="E236" s="2">
+        <v>21</v>
+      </c>
       <c r="F236" s="2" t="s">
         <v>13</v>
       </c>
@@ -15400,8 +15710,12 @@
       <c r="N236" s="10">
         <v>46227</v>
       </c>
-      <c r="O236" s="2"/>
-      <c r="P236" s="2"/>
+      <c r="O236" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P236" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q236" s="2"/>
     </row>
     <row r="237" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -15456,7 +15770,7 @@
       </c>
       <c r="Q237" s="2"/>
     </row>
-    <row r="238" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>12</v>
       </c>
@@ -15604,7 +15918,7 @@
       </c>
       <c r="Q240" s="2"/>
     </row>
-    <row r="241" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>12</v>
       </c>
@@ -15648,7 +15962,7 @@
       <c r="P241" s="2"/>
       <c r="Q241" s="2"/>
     </row>
-    <row r="242" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>12</v>
       </c>
@@ -15848,23 +16162,25 @@
       </c>
       <c r="Q245" s="2"/>
     </row>
-    <row r="246" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>173</v>
+        <v>575</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>646</v>
+        <v>576</v>
       </c>
       <c r="D246" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E246" s="2"/>
+      <c r="E246" s="2">
+        <v>21</v>
+      </c>
       <c r="F246" s="2" t="s">
-        <v>647</v>
+        <v>13</v>
       </c>
       <c r="G246" s="2" t="s">
         <v>24</v>
@@ -15873,23 +16189,29 @@
         <v>14</v>
       </c>
       <c r="I246" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J246" s="2">
         <v>1</v>
       </c>
       <c r="K246" s="11">
-        <v>21.245899999999999</v>
+        <v>10.677759999999999</v>
       </c>
       <c r="L246" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M246" s="2">
         <v>1</v>
       </c>
-      <c r="N246" s="2"/>
-      <c r="O246" s="2"/>
-      <c r="P246" s="2"/>
+      <c r="N246" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O246" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P246" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q246" s="2"/>
     </row>
     <row r="247" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16048,7 +16370,7 @@
       </c>
       <c r="Q249" s="2"/>
     </row>
-    <row r="250" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>12</v>
       </c>
@@ -16087,12 +16409,14 @@
       <c r="M250" s="2">
         <v>1</v>
       </c>
-      <c r="N250" s="2"/>
+      <c r="N250" s="10">
+        <v>46230</v>
+      </c>
       <c r="O250" s="2"/>
       <c r="P250" s="2"/>
       <c r="Q250" s="2"/>
     </row>
-    <row r="251" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>12</v>
       </c>
@@ -16136,7 +16460,7 @@
       <c r="P251" s="2"/>
       <c r="Q251" s="2"/>
     </row>
-    <row r="252" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>12</v>
       </c>
@@ -16232,7 +16556,7 @@
       </c>
       <c r="Q253" s="2"/>
     </row>
-    <row r="254" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>12</v>
       </c>
@@ -16246,7 +16570,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E254" s="2"/>
+      <c r="E254" s="2">
+        <v>21</v>
+      </c>
       <c r="F254" s="2" t="s">
         <v>213</v>
       </c>
@@ -16274,11 +16600,15 @@
       <c r="N254" s="10">
         <v>46227</v>
       </c>
-      <c r="O254" s="2"/>
-      <c r="P254" s="2"/>
+      <c r="O254" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P254" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q254" s="2"/>
     </row>
-    <row r="255" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>12</v>
       </c>
@@ -16322,7 +16652,7 @@
       <c r="P255" s="2"/>
       <c r="Q255" s="2"/>
     </row>
-    <row r="256" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>12</v>
       </c>
@@ -16366,7 +16696,7 @@
       <c r="P256" s="2"/>
       <c r="Q256" s="2"/>
     </row>
-    <row r="257" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>12</v>
       </c>
@@ -16410,7 +16740,7 @@
       <c r="P257" s="2"/>
       <c r="Q257" s="2"/>
     </row>
-    <row r="258" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>12</v>
       </c>
@@ -16454,7 +16784,7 @@
       <c r="P258" s="2"/>
       <c r="Q258" s="2"/>
     </row>
-    <row r="259" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>12</v>
       </c>
@@ -16498,7 +16828,7 @@
       <c r="P259" s="2"/>
       <c r="Q259" s="2"/>
     </row>
-    <row r="260" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>12</v>
       </c>
@@ -16542,7 +16872,7 @@
       <c r="P260" s="2"/>
       <c r="Q260" s="2"/>
     </row>
-    <row r="261" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>12</v>
       </c>
@@ -16556,7 +16886,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E261" s="2"/>
+      <c r="E261" s="2">
+        <v>21</v>
+      </c>
       <c r="F261" s="2" t="s">
         <v>216</v>
       </c>
@@ -16584,11 +16916,15 @@
       <c r="N261" s="10">
         <v>46227</v>
       </c>
-      <c r="O261" s="2"/>
-      <c r="P261" s="2"/>
+      <c r="O261" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P261" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q261" s="2"/>
     </row>
-    <row r="262" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>12</v>
       </c>
@@ -16632,7 +16968,7 @@
       <c r="P262" s="2"/>
       <c r="Q262" s="2"/>
     </row>
-    <row r="263" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>12</v>
       </c>
@@ -16676,7 +17012,7 @@
       <c r="P263" s="2"/>
       <c r="Q263" s="2"/>
     </row>
-    <row r="264" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>12</v>
       </c>
@@ -16690,7 +17026,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E264" s="2"/>
+      <c r="E264" s="2">
+        <v>21</v>
+      </c>
       <c r="F264" s="2" t="s">
         <v>219</v>
       </c>
@@ -16718,11 +17056,15 @@
       <c r="N264" s="10">
         <v>46227</v>
       </c>
-      <c r="O264" s="2"/>
-      <c r="P264" s="2"/>
+      <c r="O264" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P264" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q264" s="2"/>
     </row>
-    <row r="265" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>12</v>
       </c>
@@ -16818,7 +17160,7 @@
       </c>
       <c r="Q266" s="2"/>
     </row>
-    <row r="267" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>12</v>
       </c>
@@ -16862,7 +17204,7 @@
       <c r="P267" s="2"/>
       <c r="Q267" s="2"/>
     </row>
-    <row r="268" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>12</v>
       </c>
@@ -16906,7 +17248,7 @@
       <c r="P268" s="2"/>
       <c r="Q268" s="2"/>
     </row>
-    <row r="269" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>12</v>
       </c>
@@ -16950,7 +17292,7 @@
       <c r="P269" s="2"/>
       <c r="Q269" s="2"/>
     </row>
-    <row r="270" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>12</v>
       </c>
@@ -16994,7 +17336,7 @@
       <c r="P270" s="2"/>
       <c r="Q270" s="2"/>
     </row>
-    <row r="271" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>12</v>
       </c>
@@ -17038,7 +17380,7 @@
       <c r="P271" s="2"/>
       <c r="Q271" s="2"/>
     </row>
-    <row r="272" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>12</v>
       </c>
@@ -17082,7 +17424,7 @@
       <c r="P272" s="2"/>
       <c r="Q272" s="2"/>
     </row>
-    <row r="273" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>12</v>
       </c>
@@ -17126,7 +17468,7 @@
       <c r="P273" s="2"/>
       <c r="Q273" s="2"/>
     </row>
-    <row r="274" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>12</v>
       </c>
@@ -17170,7 +17512,7 @@
       <c r="P274" s="2"/>
       <c r="Q274" s="2"/>
     </row>
-    <row r="275" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>12</v>
       </c>
@@ -17214,7 +17556,7 @@
       <c r="P275" s="2"/>
       <c r="Q275" s="2"/>
     </row>
-    <row r="276" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>12</v>
       </c>
@@ -17258,7 +17600,7 @@
       <c r="P276" s="2"/>
       <c r="Q276" s="2"/>
     </row>
-    <row r="277" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>12</v>
       </c>
@@ -17302,7 +17644,7 @@
       <c r="P277" s="2"/>
       <c r="Q277" s="2"/>
     </row>
-    <row r="278" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>12</v>
       </c>
@@ -17316,7 +17658,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E278" s="2"/>
+      <c r="E278" s="2">
+        <v>21</v>
+      </c>
       <c r="F278" s="2" t="s">
         <v>222</v>
       </c>
@@ -17344,11 +17688,15 @@
       <c r="N278" s="10">
         <v>46227</v>
       </c>
-      <c r="O278" s="2"/>
-      <c r="P278" s="2"/>
+      <c r="O278" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P278" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q278" s="2"/>
     </row>
-    <row r="279" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>12</v>
       </c>
@@ -17392,7 +17740,7 @@
       <c r="P279" s="2"/>
       <c r="Q279" s="2"/>
     </row>
-    <row r="280" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>12</v>
       </c>
@@ -17488,23 +17836,25 @@
       </c>
       <c r="Q281" s="2"/>
     </row>
-    <row r="282" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>358</v>
+        <v>173</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>703</v>
+        <v>646</v>
       </c>
       <c r="D282" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E282" s="2"/>
+      <c r="E282" s="2">
+        <v>21</v>
+      </c>
       <c r="F282" s="2" t="s">
-        <v>704</v>
+        <v>647</v>
       </c>
       <c r="G282" s="2" t="s">
         <v>24</v>
@@ -17513,26 +17863,32 @@
         <v>14</v>
       </c>
       <c r="I282" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J282" s="2">
         <v>1</v>
       </c>
       <c r="K282" s="11">
-        <v>47.830640000000002</v>
+        <v>21.245899999999999</v>
       </c>
       <c r="L282" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M282" s="2">
-        <v>2</v>
-      </c>
-      <c r="N282" s="2"/>
-      <c r="O282" s="2"/>
-      <c r="P282" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="N282" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O282" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P282" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q282" s="2"/>
     </row>
-    <row r="283" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>12</v>
       </c>
@@ -17576,23 +17932,25 @@
       <c r="P283" s="2"/>
       <c r="Q283" s="2"/>
     </row>
-    <row r="284" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>364</v>
+        <v>257</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>707</v>
+        <v>840</v>
       </c>
       <c r="D284" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E284" s="2"/>
+      <c r="E284" s="2">
+        <v>21</v>
+      </c>
       <c r="F284" s="2" t="s">
-        <v>708</v>
+        <v>13</v>
       </c>
       <c r="G284" s="2" t="s">
         <v>24</v>
@@ -17607,36 +17965,44 @@
         <v>1</v>
       </c>
       <c r="K284" s="11">
-        <v>47.81568</v>
+        <v>6.2566800000000002</v>
       </c>
       <c r="L284" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M284" s="2">
-        <v>2</v>
-      </c>
-      <c r="N284" s="2"/>
-      <c r="O284" s="2"/>
-      <c r="P284" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="N284" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O284" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P284" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q284" s="2"/>
     </row>
-    <row r="285" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>367</v>
+        <v>556</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>709</v>
+        <v>893</v>
       </c>
       <c r="D285" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E285" s="2"/>
+      <c r="E285" s="2">
+        <v>21</v>
+      </c>
       <c r="F285" s="2" t="s">
-        <v>710</v>
+        <v>127</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>24</v>
@@ -17645,26 +18011,32 @@
         <v>14</v>
       </c>
       <c r="I285" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J285" s="2">
         <v>1</v>
       </c>
       <c r="K285" s="11">
-        <v>96.220680000000002</v>
+        <v>9.1787600000000005</v>
       </c>
       <c r="L285" s="2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M285" s="2">
-        <v>2</v>
-      </c>
-      <c r="N285" s="2"/>
-      <c r="O285" s="2"/>
-      <c r="P285" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="N285" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O285" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P285" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q285" s="2"/>
     </row>
-    <row r="286" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>12</v>
       </c>
@@ -17708,23 +18080,25 @@
       <c r="P286" s="2"/>
       <c r="Q286" s="2"/>
     </row>
-    <row r="287" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>373</v>
+        <v>305</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>713</v>
+        <v>306</v>
       </c>
       <c r="D287" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E287" s="2"/>
+      <c r="E287" s="2">
+        <v>21</v>
+      </c>
       <c r="F287" s="2" t="s">
-        <v>714</v>
+        <v>307</v>
       </c>
       <c r="G287" s="2" t="s">
         <v>24</v>
@@ -17733,42 +18107,50 @@
         <v>14</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J287" s="2">
         <v>1</v>
       </c>
       <c r="K287" s="11">
-        <v>96.220680000000002</v>
+        <v>10.317959999999999</v>
       </c>
       <c r="L287" s="2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M287" s="2">
-        <v>2</v>
-      </c>
-      <c r="N287" s="2"/>
-      <c r="O287" s="2"/>
-      <c r="P287" s="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="N287" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O287" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P287" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q287" s="2"/>
     </row>
-    <row r="288" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>376</v>
+        <v>533</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>715</v>
+        <v>534</v>
       </c>
       <c r="D288" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E288" s="2"/>
+      <c r="E288" s="2">
+        <v>21</v>
+      </c>
       <c r="F288" s="2" t="s">
-        <v>716</v>
+        <v>13</v>
       </c>
       <c r="G288" s="2" t="s">
         <v>24</v>
@@ -17783,36 +18165,44 @@
         <v>1</v>
       </c>
       <c r="K288" s="11">
-        <v>93.876760000000004</v>
+        <v>17.058309999999999</v>
       </c>
       <c r="L288" s="2">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="M288" s="2">
-        <v>2</v>
-      </c>
-      <c r="N288" s="2"/>
-      <c r="O288" s="2"/>
-      <c r="P288" s="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="N288" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O288" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P288" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q288" s="2"/>
     </row>
-    <row r="289" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>379</v>
+        <v>226</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>717</v>
+        <v>227</v>
       </c>
       <c r="D289" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E289" s="2"/>
+      <c r="E289" s="2">
+        <v>21</v>
+      </c>
       <c r="F289" s="2" t="s">
-        <v>718</v>
+        <v>228</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>24</v>
@@ -17827,17 +18217,23 @@
         <v>1</v>
       </c>
       <c r="K289" s="11">
-        <v>88.287639999999996</v>
+        <v>62.695320000000002</v>
       </c>
       <c r="L289" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M289" s="2">
         <v>2</v>
       </c>
-      <c r="N289" s="2"/>
-      <c r="O289" s="2"/>
-      <c r="P289" s="2"/>
+      <c r="N289" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O289" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P289" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q289" s="2"/>
     </row>
     <row r="290" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -17892,7 +18288,7 @@
       </c>
       <c r="Q290" s="2"/>
     </row>
-    <row r="291" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>12</v>
       </c>
@@ -18092,7 +18488,7 @@
       </c>
       <c r="Q294" s="2"/>
     </row>
-    <row r="295" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>12</v>
       </c>
@@ -18136,7 +18532,7 @@
       <c r="P295" s="2"/>
       <c r="Q295" s="2"/>
     </row>
-    <row r="296" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>12</v>
       </c>
@@ -18150,7 +18546,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E296" s="2"/>
+      <c r="E296" s="2">
+        <v>21</v>
+      </c>
       <c r="F296" s="2" t="s">
         <v>13</v>
       </c>
@@ -18178,11 +18576,15 @@
       <c r="N296" s="10">
         <v>46227</v>
       </c>
-      <c r="O296" s="2"/>
-      <c r="P296" s="2"/>
+      <c r="O296" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P296" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q296" s="2"/>
     </row>
-    <row r="297" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>12</v>
       </c>
@@ -18278,7 +18680,7 @@
       </c>
       <c r="Q298" s="2"/>
     </row>
-    <row r="299" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>12</v>
       </c>
@@ -18322,7 +18724,7 @@
       <c r="P299" s="2"/>
       <c r="Q299" s="2"/>
     </row>
-    <row r="300" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>12</v>
       </c>
@@ -18366,7 +18768,7 @@
       <c r="P300" s="2"/>
       <c r="Q300" s="2"/>
     </row>
-    <row r="301" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>12</v>
       </c>
@@ -18410,7 +18812,7 @@
       <c r="P301" s="2"/>
       <c r="Q301" s="2"/>
     </row>
-    <row r="302" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>12</v>
       </c>
@@ -18506,7 +18908,7 @@
       </c>
       <c r="Q303" s="2"/>
     </row>
-    <row r="304" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>12</v>
       </c>
@@ -18550,7 +18952,7 @@
       <c r="P304" s="2"/>
       <c r="Q304" s="2"/>
     </row>
-    <row r="305" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>12</v>
       </c>
@@ -18594,7 +18996,7 @@
       <c r="P305" s="2"/>
       <c r="Q305" s="2"/>
     </row>
-    <row r="306" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>12</v>
       </c>
@@ -18638,7 +19040,7 @@
       <c r="P306" s="2"/>
       <c r="Q306" s="2"/>
     </row>
-    <row r="307" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>12</v>
       </c>
@@ -18682,7 +19084,7 @@
       <c r="P307" s="2"/>
       <c r="Q307" s="2"/>
     </row>
-    <row r="308" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>12</v>
       </c>
@@ -18726,7 +19128,7 @@
       <c r="P308" s="2"/>
       <c r="Q308" s="2"/>
     </row>
-    <row r="309" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>12</v>
       </c>
@@ -18874,7 +19276,7 @@
       </c>
       <c r="Q311" s="2"/>
     </row>
-    <row r="312" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>12</v>
       </c>
@@ -18888,7 +19290,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E312" s="2"/>
+      <c r="E312" s="2">
+        <v>21</v>
+      </c>
       <c r="F312" s="2" t="s">
         <v>277</v>
       </c>
@@ -18916,11 +19320,15 @@
       <c r="N312" s="10">
         <v>46227</v>
       </c>
-      <c r="O312" s="2"/>
-      <c r="P312" s="2"/>
+      <c r="O312" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P312" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q312" s="2"/>
     </row>
-    <row r="313" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>12</v>
       </c>
@@ -18934,7 +19342,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E313" s="2"/>
+      <c r="E313" s="2">
+        <v>21</v>
+      </c>
       <c r="F313" s="2" t="s">
         <v>13</v>
       </c>
@@ -18962,11 +19372,15 @@
       <c r="N313" s="10">
         <v>46227</v>
       </c>
-      <c r="O313" s="2"/>
-      <c r="P313" s="2"/>
+      <c r="O313" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P313" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q313" s="2"/>
     </row>
-    <row r="314" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>12</v>
       </c>
@@ -19010,7 +19424,7 @@
       <c r="P314" s="2"/>
       <c r="Q314" s="2"/>
     </row>
-    <row r="315" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>12</v>
       </c>
@@ -19024,7 +19438,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E315" s="2"/>
+      <c r="E315" s="2">
+        <v>21</v>
+      </c>
       <c r="F315" s="2" t="s">
         <v>310</v>
       </c>
@@ -19052,11 +19468,15 @@
       <c r="N315" s="10">
         <v>46227</v>
       </c>
-      <c r="O315" s="2"/>
-      <c r="P315" s="2"/>
+      <c r="O315" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P315" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q315" s="2"/>
     </row>
-    <row r="316" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>12</v>
       </c>
@@ -19100,7 +19520,7 @@
       <c r="P316" s="2"/>
       <c r="Q316" s="2"/>
     </row>
-    <row r="317" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>12</v>
       </c>
@@ -19114,7 +19534,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E317" s="2"/>
+      <c r="E317" s="2">
+        <v>21</v>
+      </c>
       <c r="F317" s="2" t="s">
         <v>316</v>
       </c>
@@ -19142,11 +19564,15 @@
       <c r="N317" s="10">
         <v>46227</v>
       </c>
-      <c r="O317" s="2"/>
-      <c r="P317" s="2"/>
+      <c r="O317" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P317" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q317" s="2"/>
     </row>
-    <row r="318" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>12</v>
       </c>
@@ -19190,7 +19616,7 @@
       <c r="P318" s="2"/>
       <c r="Q318" s="2"/>
     </row>
-    <row r="319" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>12</v>
       </c>
@@ -19204,7 +19630,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E319" s="2"/>
+      <c r="E319" s="2">
+        <v>21</v>
+      </c>
       <c r="F319" s="2" t="s">
         <v>319</v>
       </c>
@@ -19232,8 +19660,12 @@
       <c r="N319" s="10">
         <v>46227</v>
       </c>
-      <c r="O319" s="2"/>
-      <c r="P319" s="2"/>
+      <c r="O319" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P319" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q319" s="2"/>
     </row>
     <row r="320" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19288,7 +19720,7 @@
       </c>
       <c r="Q320" s="2"/>
     </row>
-    <row r="321" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>12</v>
       </c>
@@ -19302,7 +19734,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E321" s="2"/>
+      <c r="E321" s="2">
+        <v>21</v>
+      </c>
       <c r="F321" s="2" t="s">
         <v>13</v>
       </c>
@@ -19330,11 +19764,15 @@
       <c r="N321" s="10">
         <v>46227</v>
       </c>
-      <c r="O321" s="2"/>
-      <c r="P321" s="2"/>
+      <c r="O321" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P321" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q321" s="2"/>
     </row>
-    <row r="322" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>12</v>
       </c>
@@ -19378,23 +19816,25 @@
       <c r="P322" s="2"/>
       <c r="Q322" s="2"/>
     </row>
-    <row r="323" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>543</v>
+        <v>358</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>770</v>
+        <v>703</v>
       </c>
       <c r="D323" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E323" s="2"/>
+      <c r="E323" s="2">
+        <v>21</v>
+      </c>
       <c r="F323" s="2" t="s">
-        <v>13</v>
+        <v>704</v>
       </c>
       <c r="G323" s="2" t="s">
         <v>24</v>
@@ -19409,17 +19849,23 @@
         <v>1</v>
       </c>
       <c r="K323" s="11">
-        <v>5.0014000000000003</v>
+        <v>47.830640000000002</v>
       </c>
       <c r="L323" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M323" s="2">
         <v>2</v>
       </c>
-      <c r="N323" s="2"/>
-      <c r="O323" s="2"/>
-      <c r="P323" s="2"/>
+      <c r="N323" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O323" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P323" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q323" s="2"/>
     </row>
     <row r="324" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19474,7 +19920,7 @@
       </c>
       <c r="Q324" s="2"/>
     </row>
-    <row r="325" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>12</v>
       </c>
@@ -19518,7 +19964,7 @@
       <c r="P325" s="2"/>
       <c r="Q325" s="2"/>
     </row>
-    <row r="326" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>12</v>
       </c>
@@ -19562,7 +20008,7 @@
       <c r="P326" s="2"/>
       <c r="Q326" s="2"/>
     </row>
-    <row r="327" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>12</v>
       </c>
@@ -19606,7 +20052,7 @@
       <c r="P327" s="2"/>
       <c r="Q327" s="2"/>
     </row>
-    <row r="328" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>12</v>
       </c>
@@ -19650,7 +20096,7 @@
       <c r="P328" s="2"/>
       <c r="Q328" s="2"/>
     </row>
-    <row r="329" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>12</v>
       </c>
@@ -19689,12 +20135,14 @@
       <c r="M329" s="2">
         <v>1</v>
       </c>
-      <c r="N329" s="2"/>
+      <c r="N329" s="10">
+        <v>46230</v>
+      </c>
       <c r="O329" s="2"/>
       <c r="P329" s="2"/>
       <c r="Q329" s="2"/>
     </row>
-    <row r="330" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>12</v>
       </c>
@@ -19738,7 +20186,7 @@
       <c r="P330" s="2"/>
       <c r="Q330" s="2"/>
     </row>
-    <row r="331" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>12</v>
       </c>
@@ -19782,7 +20230,7 @@
       <c r="P331" s="2"/>
       <c r="Q331" s="2"/>
     </row>
-    <row r="332" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>12</v>
       </c>
@@ -19796,7 +20244,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E332" s="2"/>
+      <c r="E332" s="2">
+        <v>21</v>
+      </c>
       <c r="F332" s="2" t="s">
         <v>697</v>
       </c>
@@ -19824,8 +20274,12 @@
       <c r="N332" s="10">
         <v>46227</v>
       </c>
-      <c r="O332" s="2"/>
-      <c r="P332" s="2"/>
+      <c r="O332" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P332" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q332" s="2"/>
     </row>
     <row r="333" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19880,7 +20334,7 @@
       </c>
       <c r="Q333" s="2"/>
     </row>
-    <row r="334" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>12</v>
       </c>
@@ -19924,7 +20378,7 @@
       <c r="P334" s="2"/>
       <c r="Q334" s="2"/>
     </row>
-    <row r="335" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>12</v>
       </c>
@@ -19963,7 +20417,9 @@
       <c r="M335" s="2">
         <v>0.5</v>
       </c>
-      <c r="N335" s="2"/>
+      <c r="N335" s="10">
+        <v>46230</v>
+      </c>
       <c r="O335" s="2"/>
       <c r="P335" s="2"/>
       <c r="Q335" s="2"/>
@@ -20020,7 +20476,7 @@
       </c>
       <c r="Q336" s="2"/>
     </row>
-    <row r="337" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>12</v>
       </c>
@@ -20064,7 +20520,7 @@
       <c r="P337" s="2"/>
       <c r="Q337" s="2"/>
     </row>
-    <row r="338" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>12</v>
       </c>
@@ -20108,7 +20564,7 @@
       <c r="P338" s="2"/>
       <c r="Q338" s="2"/>
     </row>
-    <row r="339" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>12</v>
       </c>
@@ -20672,7 +21128,7 @@
       </c>
       <c r="Q349" s="2"/>
     </row>
-    <row r="350" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>12</v>
       </c>
@@ -20716,7 +21172,7 @@
       <c r="P350" s="2"/>
       <c r="Q350" s="2"/>
     </row>
-    <row r="351" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>12</v>
       </c>
@@ -20968,7 +21424,7 @@
       </c>
       <c r="Q355" s="2"/>
     </row>
-    <row r="356" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>12</v>
       </c>
@@ -21012,7 +21468,7 @@
       <c r="P356" s="2"/>
       <c r="Q356" s="2"/>
     </row>
-    <row r="357" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>12</v>
       </c>
@@ -21051,7 +21507,9 @@
       <c r="M357" s="2">
         <v>1</v>
       </c>
-      <c r="N357" s="2"/>
+      <c r="N357" s="10">
+        <v>46230</v>
+      </c>
       <c r="O357" s="2"/>
       <c r="P357" s="2"/>
       <c r="Q357" s="2"/>
@@ -21108,7 +21566,7 @@
       </c>
       <c r="Q358" s="2"/>
     </row>
-    <row r="359" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>12</v>
       </c>
@@ -21204,7 +21662,7 @@
       </c>
       <c r="Q360" s="2"/>
     </row>
-    <row r="361" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>12</v>
       </c>
@@ -21218,7 +21676,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E361" s="2"/>
+      <c r="E361" s="2">
+        <v>21</v>
+      </c>
       <c r="F361" s="2" t="s">
         <v>127</v>
       </c>
@@ -21246,11 +21706,15 @@
       <c r="N361" s="10">
         <v>46227</v>
       </c>
-      <c r="O361" s="2"/>
-      <c r="P361" s="2"/>
+      <c r="O361" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P361" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q361" s="2"/>
     </row>
-    <row r="362" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>12</v>
       </c>
@@ -21346,7 +21810,7 @@
       </c>
       <c r="Q363" s="2"/>
     </row>
-    <row r="364" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>12</v>
       </c>
@@ -21360,7 +21824,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E364" s="2"/>
+      <c r="E364" s="2">
+        <v>21</v>
+      </c>
       <c r="F364" s="2" t="s">
         <v>352</v>
       </c>
@@ -21388,11 +21854,15 @@
       <c r="N364" s="10">
         <v>46227</v>
       </c>
-      <c r="O364" s="2"/>
-      <c r="P364" s="2"/>
+      <c r="O364" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P364" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q364" s="2"/>
     </row>
-    <row r="365" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>12</v>
       </c>
@@ -21436,7 +21906,7 @@
       <c r="P365" s="2"/>
       <c r="Q365" s="2"/>
     </row>
-    <row r="366" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>12</v>
       </c>
@@ -21480,7 +21950,7 @@
       <c r="P366" s="2"/>
       <c r="Q366" s="2"/>
     </row>
-    <row r="367" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>12</v>
       </c>
@@ -21524,23 +21994,25 @@
       <c r="P367" s="2"/>
       <c r="Q367" s="2"/>
     </row>
-    <row r="368" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>257</v>
+        <v>364</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>840</v>
+        <v>707</v>
       </c>
       <c r="D368" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E368" s="2"/>
+      <c r="E368" s="2">
+        <v>21</v>
+      </c>
       <c r="F368" s="2" t="s">
-        <v>13</v>
+        <v>708</v>
       </c>
       <c r="G368" s="2" t="s">
         <v>24</v>
@@ -21555,20 +22027,26 @@
         <v>1</v>
       </c>
       <c r="K368" s="11">
-        <v>6.2566800000000002</v>
+        <v>47.81568</v>
       </c>
       <c r="L368" s="2">
+        <v>12</v>
+      </c>
+      <c r="M368" s="2">
         <v>2</v>
       </c>
-      <c r="M368" s="2">
-        <v>1</v>
-      </c>
-      <c r="N368" s="2"/>
-      <c r="O368" s="2"/>
-      <c r="P368" s="2"/>
+      <c r="N368" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O368" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P368" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q368" s="2"/>
     </row>
-    <row r="369" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>12</v>
       </c>
@@ -21612,7 +22090,7 @@
       <c r="P369" s="2"/>
       <c r="Q369" s="2"/>
     </row>
-    <row r="370" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>12</v>
       </c>
@@ -21656,7 +22134,7 @@
       <c r="P370" s="2"/>
       <c r="Q370" s="2"/>
     </row>
-    <row r="371" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>12</v>
       </c>
@@ -21700,7 +22178,7 @@
       <c r="P371" s="2"/>
       <c r="Q371" s="2"/>
     </row>
-    <row r="372" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>12</v>
       </c>
@@ -21714,7 +22192,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E372" s="2"/>
+      <c r="E372" s="2">
+        <v>21</v>
+      </c>
       <c r="F372" s="2" t="s">
         <v>127</v>
       </c>
@@ -21742,11 +22222,15 @@
       <c r="N372" s="10">
         <v>46227</v>
       </c>
-      <c r="O372" s="2"/>
-      <c r="P372" s="2"/>
+      <c r="O372" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P372" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q372" s="2"/>
     </row>
-    <row r="373" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>12</v>
       </c>
@@ -21790,7 +22274,7 @@
       <c r="P373" s="2"/>
       <c r="Q373" s="2"/>
     </row>
-    <row r="374" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>12</v>
       </c>
@@ -21886,7 +22370,7 @@
       </c>
       <c r="Q375" s="2"/>
     </row>
-    <row r="376" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>12</v>
       </c>
@@ -21900,7 +22384,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E376" s="2"/>
+      <c r="E376" s="2">
+        <v>21</v>
+      </c>
       <c r="F376" s="2" t="s">
         <v>13</v>
       </c>
@@ -21928,8 +22414,12 @@
       <c r="N376" s="10">
         <v>46227</v>
       </c>
-      <c r="O376" s="2"/>
-      <c r="P376" s="2"/>
+      <c r="O376" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P376" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q376" s="2"/>
     </row>
     <row r="377" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -21984,7 +22474,7 @@
       </c>
       <c r="Q377" s="2"/>
     </row>
-    <row r="378" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>12</v>
       </c>
@@ -22028,7 +22518,7 @@
       <c r="P378" s="2"/>
       <c r="Q378" s="2"/>
     </row>
-    <row r="379" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>12</v>
       </c>
@@ -22072,7 +22562,7 @@
       <c r="P379" s="2"/>
       <c r="Q379" s="2"/>
     </row>
-    <row r="380" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>12</v>
       </c>
@@ -22116,7 +22606,7 @@
       <c r="P380" s="2"/>
       <c r="Q380" s="2"/>
     </row>
-    <row r="381" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>12</v>
       </c>
@@ -22160,7 +22650,7 @@
       <c r="P381" s="2"/>
       <c r="Q381" s="2"/>
     </row>
-    <row r="382" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>12</v>
       </c>
@@ -22204,7 +22694,7 @@
       <c r="P382" s="2"/>
       <c r="Q382" s="2"/>
     </row>
-    <row r="383" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>12</v>
       </c>
@@ -22248,7 +22738,7 @@
       <c r="P383" s="2"/>
       <c r="Q383" s="2"/>
     </row>
-    <row r="384" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>12</v>
       </c>
@@ -22292,7 +22782,7 @@
       <c r="P384" s="2"/>
       <c r="Q384" s="2"/>
     </row>
-    <row r="385" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>12</v>
       </c>
@@ -22336,7 +22826,7 @@
       <c r="P385" s="2"/>
       <c r="Q385" s="2"/>
     </row>
-    <row r="386" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>12</v>
       </c>
@@ -22380,7 +22870,7 @@
       <c r="P386" s="2"/>
       <c r="Q386" s="2"/>
     </row>
-    <row r="387" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>12</v>
       </c>
@@ -22424,7 +22914,7 @@
       <c r="P387" s="2"/>
       <c r="Q387" s="2"/>
     </row>
-    <row r="388" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>12</v>
       </c>
@@ -22438,7 +22928,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E388" s="2"/>
+      <c r="E388" s="2">
+        <v>21</v>
+      </c>
       <c r="F388" s="2" t="s">
         <v>13</v>
       </c>
@@ -22466,11 +22958,15 @@
       <c r="N388" s="10">
         <v>46227</v>
       </c>
-      <c r="O388" s="2"/>
-      <c r="P388" s="2"/>
+      <c r="O388" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P388" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q388" s="2"/>
     </row>
-    <row r="389" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>12</v>
       </c>
@@ -22618,7 +23114,7 @@
       </c>
       <c r="Q391" s="2"/>
     </row>
-    <row r="392" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>12</v>
       </c>
@@ -22662,7 +23158,7 @@
       <c r="P392" s="2"/>
       <c r="Q392" s="2"/>
     </row>
-    <row r="393" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>12</v>
       </c>
@@ -22676,7 +23172,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E393" s="2"/>
+      <c r="E393" s="2">
+        <v>21</v>
+      </c>
       <c r="F393" s="2" t="s">
         <v>13</v>
       </c>
@@ -22704,8 +23202,12 @@
       <c r="N393" s="10">
         <v>46227</v>
       </c>
-      <c r="O393" s="2"/>
-      <c r="P393" s="2"/>
+      <c r="O393" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P393" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q393" s="2"/>
     </row>
     <row r="394" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -22812,7 +23314,7 @@
       </c>
       <c r="Q395" s="2"/>
     </row>
-    <row r="396" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>12</v>
       </c>
@@ -22908,7 +23410,7 @@
       </c>
       <c r="Q397" s="2"/>
     </row>
-    <row r="398" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>12</v>
       </c>
@@ -23004,7 +23506,7 @@
       </c>
       <c r="Q399" s="2"/>
     </row>
-    <row r="400" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>12</v>
       </c>
@@ -23048,7 +23550,7 @@
       <c r="P400" s="2"/>
       <c r="Q400" s="2"/>
     </row>
-    <row r="401" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>12</v>
       </c>
@@ -23144,7 +23646,7 @@
       </c>
       <c r="Q402" s="2"/>
     </row>
-    <row r="403" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>12</v>
       </c>
@@ -23188,7 +23690,7 @@
       <c r="P403" s="2"/>
       <c r="Q403" s="2"/>
     </row>
-    <row r="404" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>12</v>
       </c>
@@ -23284,7 +23786,7 @@
       </c>
       <c r="Q405" s="2"/>
     </row>
-    <row r="406" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>12</v>
       </c>
@@ -23328,23 +23830,25 @@
       <c r="P406" s="2"/>
       <c r="Q406" s="2"/>
     </row>
-    <row r="407" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>556</v>
+        <v>367</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>893</v>
+        <v>709</v>
       </c>
       <c r="D407" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E407" s="2"/>
+      <c r="E407" s="2">
+        <v>21</v>
+      </c>
       <c r="F407" s="2" t="s">
-        <v>127</v>
+        <v>710</v>
       </c>
       <c r="G407" s="2" t="s">
         <v>24</v>
@@ -23353,26 +23857,32 @@
         <v>14</v>
       </c>
       <c r="I407" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J407" s="2">
         <v>1</v>
       </c>
       <c r="K407" s="11">
-        <v>9.1787600000000005</v>
+        <v>96.220680000000002</v>
       </c>
       <c r="L407" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M407" s="2">
-        <v>1</v>
-      </c>
-      <c r="N407" s="2"/>
-      <c r="O407" s="2"/>
-      <c r="P407" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="N407" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O407" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P407" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q407" s="2"/>
     </row>
-    <row r="408" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>12</v>
       </c>
@@ -23386,7 +23896,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E408" s="2"/>
+      <c r="E408" s="2">
+        <v>21</v>
+      </c>
       <c r="F408" s="2" t="s">
         <v>959</v>
       </c>
@@ -23414,11 +23926,15 @@
       <c r="N408" s="10">
         <v>46227</v>
       </c>
-      <c r="O408" s="2"/>
-      <c r="P408" s="2"/>
+      <c r="O408" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P408" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q408" s="2"/>
     </row>
-    <row r="409" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>12</v>
       </c>
@@ -23457,12 +23973,14 @@
       <c r="M409" s="2">
         <v>1</v>
       </c>
-      <c r="N409" s="2"/>
+      <c r="N409" s="10">
+        <v>46230</v>
+      </c>
       <c r="O409" s="2"/>
       <c r="P409" s="2"/>
       <c r="Q409" s="2"/>
     </row>
-    <row r="410" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>12</v>
       </c>
@@ -23506,7 +24024,7 @@
       <c r="P410" s="2"/>
       <c r="Q410" s="2"/>
     </row>
-    <row r="411" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>12</v>
       </c>
@@ -23520,7 +24038,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E411" s="2"/>
+      <c r="E411" s="2">
+        <v>21</v>
+      </c>
       <c r="F411" s="2" t="s">
         <v>445</v>
       </c>
@@ -23548,8 +24068,12 @@
       <c r="N411" s="10">
         <v>46227</v>
       </c>
-      <c r="O411" s="2"/>
-      <c r="P411" s="2"/>
+      <c r="O411" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P411" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q411" s="2"/>
     </row>
     <row r="412" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23708,7 +24232,7 @@
       </c>
       <c r="Q414" s="2"/>
     </row>
-    <row r="415" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>12</v>
       </c>
@@ -23752,7 +24276,7 @@
       <c r="P415" s="2"/>
       <c r="Q415" s="2"/>
     </row>
-    <row r="416" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>12</v>
       </c>
@@ -23796,7 +24320,7 @@
       <c r="P416" s="2"/>
       <c r="Q416" s="2"/>
     </row>
-    <row r="417" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>12</v>
       </c>
@@ -23840,7 +24364,7 @@
       <c r="P417" s="2"/>
       <c r="Q417" s="2"/>
     </row>
-    <row r="418" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>12</v>
       </c>
@@ -23884,7 +24408,7 @@
       <c r="P418" s="2"/>
       <c r="Q418" s="2"/>
     </row>
-    <row r="419" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>12</v>
       </c>
@@ -23928,7 +24452,7 @@
       <c r="P419" s="2"/>
       <c r="Q419" s="2"/>
     </row>
-    <row r="420" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>12</v>
       </c>
@@ -23972,7 +24496,7 @@
       <c r="P420" s="2"/>
       <c r="Q420" s="2"/>
     </row>
-    <row r="421" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>12</v>
       </c>
@@ -24016,7 +24540,7 @@
       <c r="P421" s="2"/>
       <c r="Q421" s="2"/>
     </row>
-    <row r="422" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>12</v>
       </c>
@@ -24112,7 +24636,7 @@
       </c>
       <c r="Q423" s="2"/>
     </row>
-    <row r="424" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>12</v>
       </c>
@@ -24151,12 +24675,14 @@
       <c r="M424" s="2">
         <v>1</v>
       </c>
-      <c r="N424" s="2"/>
+      <c r="N424" s="10">
+        <v>46230</v>
+      </c>
       <c r="O424" s="2"/>
       <c r="P424" s="2"/>
       <c r="Q424" s="2"/>
     </row>
-    <row r="425" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>12</v>
       </c>
@@ -24170,7 +24696,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E425" s="2"/>
+      <c r="E425" s="2">
+        <v>21</v>
+      </c>
       <c r="F425" s="2" t="s">
         <v>127</v>
       </c>
@@ -24198,11 +24726,15 @@
       <c r="N425" s="10">
         <v>46227</v>
       </c>
-      <c r="O425" s="2"/>
-      <c r="P425" s="2"/>
+      <c r="O425" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P425" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q425" s="2"/>
     </row>
-    <row r="426" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>12</v>
       </c>
@@ -24246,7 +24778,7 @@
       <c r="P426" s="2"/>
       <c r="Q426" s="2"/>
     </row>
-    <row r="427" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>12</v>
       </c>
@@ -24260,7 +24792,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E427" s="2"/>
+      <c r="E427" s="2">
+        <v>21</v>
+      </c>
       <c r="F427" s="2" t="s">
         <v>127</v>
       </c>
@@ -24288,8 +24822,12 @@
       <c r="N427" s="10">
         <v>46227</v>
       </c>
-      <c r="O427" s="2"/>
-      <c r="P427" s="2"/>
+      <c r="O427" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P427" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q427" s="2"/>
     </row>
     <row r="428" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -24396,23 +24934,25 @@
       </c>
       <c r="Q429" s="2"/>
     </row>
-    <row r="430" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>152</v>
+        <v>373</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>927</v>
+        <v>713</v>
       </c>
       <c r="D430" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E430" s="2"/>
+      <c r="E430" s="2">
+        <v>21</v>
+      </c>
       <c r="F430" s="2" t="s">
-        <v>928</v>
+        <v>714</v>
       </c>
       <c r="G430" s="2" t="s">
         <v>24</v>
@@ -24427,20 +24967,26 @@
         <v>1</v>
       </c>
       <c r="K430" s="11">
-        <v>11.249700000000001</v>
+        <v>96.220680000000002</v>
       </c>
       <c r="L430" s="2">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="M430" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="N430" s="2"/>
-      <c r="O430" s="2"/>
-      <c r="P430" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="N430" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O430" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P430" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q430" s="2"/>
     </row>
-    <row r="431" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>12</v>
       </c>
@@ -24484,7 +25030,7 @@
       <c r="P431" s="2"/>
       <c r="Q431" s="2"/>
     </row>
-    <row r="432" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>12</v>
       </c>
@@ -24528,7 +25074,7 @@
       <c r="P432" s="2"/>
       <c r="Q432" s="2"/>
     </row>
-    <row r="433" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>12</v>
       </c>
@@ -24624,7 +25170,7 @@
       </c>
       <c r="Q434" s="2"/>
     </row>
-    <row r="435" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>12</v>
       </c>
@@ -24638,7 +25184,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E435" s="2"/>
+      <c r="E435" s="2">
+        <v>21</v>
+      </c>
       <c r="F435" s="2" t="s">
         <v>127</v>
       </c>
@@ -24666,11 +25214,15 @@
       <c r="N435" s="10">
         <v>46227</v>
       </c>
-      <c r="O435" s="2"/>
-      <c r="P435" s="2"/>
+      <c r="O435" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P435" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q435" s="2"/>
     </row>
-    <row r="436" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>12</v>
       </c>
@@ -24766,7 +25318,7 @@
       </c>
       <c r="Q437" s="2"/>
     </row>
-    <row r="438" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>12</v>
       </c>
@@ -24780,7 +25332,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E438" s="2"/>
+      <c r="E438" s="2">
+        <v>21</v>
+      </c>
       <c r="F438" s="2" t="s">
         <v>127</v>
       </c>
@@ -24808,11 +25362,15 @@
       <c r="N438" s="10">
         <v>46227</v>
       </c>
-      <c r="O438" s="2"/>
-      <c r="P438" s="2"/>
+      <c r="O438" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P438" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q438" s="2"/>
     </row>
-    <row r="439" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>12</v>
       </c>
@@ -24908,7 +25466,7 @@
       </c>
       <c r="Q440" s="2"/>
     </row>
-    <row r="441" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>12</v>
       </c>
@@ -24952,7 +25510,7 @@
       <c r="P441" s="2"/>
       <c r="Q441" s="2"/>
     </row>
-    <row r="442" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>12</v>
       </c>
@@ -24996,7 +25554,7 @@
       <c r="P442" s="2"/>
       <c r="Q442" s="2"/>
     </row>
-    <row r="443" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>12</v>
       </c>
@@ -25040,7 +25598,7 @@
       <c r="P443" s="2"/>
       <c r="Q443" s="2"/>
     </row>
-    <row r="444" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>12</v>
       </c>
@@ -25084,7 +25642,7 @@
       <c r="P444" s="2"/>
       <c r="Q444" s="2"/>
     </row>
-    <row r="445" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>12</v>
       </c>
@@ -25098,7 +25656,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E445" s="2"/>
+      <c r="E445" s="2">
+        <v>21</v>
+      </c>
       <c r="F445" s="2" t="s">
         <v>127</v>
       </c>
@@ -25126,8 +25686,12 @@
       <c r="N445" s="10">
         <v>46227</v>
       </c>
-      <c r="O445" s="2"/>
-      <c r="P445" s="2"/>
+      <c r="O445" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P445" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q445" s="2"/>
     </row>
     <row r="446" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -25182,7 +25746,7 @@
       </c>
       <c r="Q446" s="2"/>
     </row>
-    <row r="447" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>12</v>
       </c>
@@ -25278,7 +25842,7 @@
       </c>
       <c r="Q448" s="2"/>
     </row>
-    <row r="449" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>12</v>
       </c>
@@ -25374,7 +25938,7 @@
       </c>
       <c r="Q450" s="2"/>
     </row>
-    <row r="451" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>12</v>
       </c>
@@ -25388,7 +25952,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E451" s="2"/>
+      <c r="E451" s="2">
+        <v>21</v>
+      </c>
       <c r="F451" s="2" t="s">
         <v>127</v>
       </c>
@@ -25416,11 +25982,15 @@
       <c r="N451" s="10">
         <v>46227</v>
       </c>
-      <c r="O451" s="2"/>
-      <c r="P451" s="2"/>
+      <c r="O451" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P451" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q451" s="2"/>
     </row>
-    <row r="452" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>12</v>
       </c>
@@ -25434,7 +26004,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E452" s="2"/>
+      <c r="E452" s="2">
+        <v>21</v>
+      </c>
       <c r="F452" s="2" t="s">
         <v>127</v>
       </c>
@@ -25462,11 +26034,15 @@
       <c r="N452" s="10">
         <v>46227</v>
       </c>
-      <c r="O452" s="2"/>
-      <c r="P452" s="2"/>
+      <c r="O452" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P452" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q452" s="2"/>
     </row>
-    <row r="453" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>12</v>
       </c>
@@ -25480,7 +26056,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E453" s="2"/>
+      <c r="E453" s="2">
+        <v>21</v>
+      </c>
       <c r="F453" s="2" t="s">
         <v>127</v>
       </c>
@@ -25508,11 +26086,15 @@
       <c r="N453" s="10">
         <v>46227</v>
       </c>
-      <c r="O453" s="2"/>
-      <c r="P453" s="2"/>
+      <c r="O453" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P453" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q453" s="2"/>
     </row>
-    <row r="454" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>12</v>
       </c>
@@ -25526,7 +26108,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E454" s="2"/>
+      <c r="E454" s="2">
+        <v>21</v>
+      </c>
       <c r="F454" s="2" t="s">
         <v>13</v>
       </c>
@@ -25554,11 +26138,15 @@
       <c r="N454" s="10">
         <v>46227</v>
       </c>
-      <c r="O454" s="2"/>
-      <c r="P454" s="2"/>
+      <c r="O454" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P454" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q454" s="2"/>
     </row>
-    <row r="455" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>12</v>
       </c>
@@ -25572,7 +26160,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E455" s="2"/>
+      <c r="E455" s="2">
+        <v>21</v>
+      </c>
       <c r="F455" s="2" t="s">
         <v>468</v>
       </c>
@@ -25600,11 +26190,15 @@
       <c r="N455" s="10">
         <v>46227</v>
       </c>
-      <c r="O455" s="2"/>
-      <c r="P455" s="2"/>
+      <c r="O455" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P455" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q455" s="2"/>
     </row>
-    <row r="456" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>12</v>
       </c>
@@ -25648,7 +26242,7 @@
       <c r="P456" s="2"/>
       <c r="Q456" s="2"/>
     </row>
-    <row r="457" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>12</v>
       </c>
@@ -25692,7 +26286,7 @@
       <c r="P457" s="2"/>
       <c r="Q457" s="2"/>
     </row>
-    <row r="458" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>12</v>
       </c>
@@ -25706,7 +26300,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E458" s="2"/>
+      <c r="E458" s="2">
+        <v>21</v>
+      </c>
       <c r="F458" s="2" t="s">
         <v>477</v>
       </c>
@@ -25734,11 +26330,15 @@
       <c r="N458" s="10">
         <v>46227</v>
       </c>
-      <c r="O458" s="2"/>
-      <c r="P458" s="2"/>
+      <c r="O458" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P458" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q458" s="2"/>
     </row>
-    <row r="459" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>12</v>
       </c>
@@ -25782,7 +26382,7 @@
       <c r="P459" s="2"/>
       <c r="Q459" s="2"/>
     </row>
-    <row r="460" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>12</v>
       </c>
@@ -25796,7 +26396,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E460" s="2"/>
+      <c r="E460" s="2">
+        <v>21</v>
+      </c>
       <c r="F460" s="2" t="s">
         <v>502</v>
       </c>
@@ -25824,11 +26426,15 @@
       <c r="N460" s="10">
         <v>46227</v>
       </c>
-      <c r="O460" s="2"/>
-      <c r="P460" s="2"/>
+      <c r="O460" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P460" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q460" s="2"/>
     </row>
-    <row r="461" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>12</v>
       </c>
@@ -25872,7 +26478,7 @@
       <c r="P461" s="2"/>
       <c r="Q461" s="2"/>
     </row>
-    <row r="462" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>12</v>
       </c>
@@ -25886,7 +26492,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E462" s="2"/>
+      <c r="E462" s="2">
+        <v>21</v>
+      </c>
       <c r="F462" s="2" t="s">
         <v>505</v>
       </c>
@@ -25914,11 +26522,15 @@
       <c r="N462" s="10">
         <v>46227</v>
       </c>
-      <c r="O462" s="2"/>
-      <c r="P462" s="2"/>
+      <c r="O462" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P462" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q462" s="2"/>
     </row>
-    <row r="463" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>12</v>
       </c>
@@ -25962,7 +26574,7 @@
       <c r="P463" s="2"/>
       <c r="Q463" s="2"/>
     </row>
-    <row r="464" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>12</v>
       </c>
@@ -26006,7 +26618,7 @@
       <c r="P464" s="2"/>
       <c r="Q464" s="2"/>
     </row>
-    <row r="465" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>12</v>
       </c>
@@ -26050,7 +26662,7 @@
       <c r="P465" s="2"/>
       <c r="Q465" s="2"/>
     </row>
-    <row r="466" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>12</v>
       </c>
@@ -26094,7 +26706,7 @@
       <c r="P466" s="2"/>
       <c r="Q466" s="2"/>
     </row>
-    <row r="467" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>12</v>
       </c>
@@ -26138,7 +26750,7 @@
       <c r="P467" s="2"/>
       <c r="Q467" s="2"/>
     </row>
-    <row r="468" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>12</v>
       </c>
@@ -26177,12 +26789,14 @@
       <c r="M468" s="2">
         <v>1</v>
       </c>
-      <c r="N468" s="2"/>
+      <c r="N468" s="10">
+        <v>46230</v>
+      </c>
       <c r="O468" s="2"/>
       <c r="P468" s="2"/>
       <c r="Q468" s="2"/>
     </row>
-    <row r="469" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>12</v>
       </c>
@@ -26226,7 +26840,7 @@
       <c r="P469" s="2"/>
       <c r="Q469" s="2"/>
     </row>
-    <row r="470" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>12</v>
       </c>
@@ -26374,7 +26988,7 @@
       </c>
       <c r="Q472" s="2"/>
     </row>
-    <row r="473" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>12</v>
       </c>
@@ -26470,7 +27084,7 @@
       </c>
       <c r="Q474" s="2"/>
     </row>
-    <row r="475" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>12</v>
       </c>
@@ -26509,7 +27123,9 @@
       <c r="M475" s="2">
         <v>1</v>
       </c>
-      <c r="N475" s="2"/>
+      <c r="N475" s="10">
+        <v>46230</v>
+      </c>
       <c r="O475" s="2"/>
       <c r="P475" s="2"/>
       <c r="Q475" s="2"/>
@@ -26566,7 +27182,7 @@
       </c>
       <c r="Q476" s="2"/>
     </row>
-    <row r="477" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>12</v>
       </c>
@@ -26610,7 +27226,7 @@
       <c r="P477" s="2"/>
       <c r="Q477" s="2"/>
     </row>
-    <row r="478" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>12</v>
       </c>
@@ -26654,7 +27270,7 @@
       <c r="P478" s="2"/>
       <c r="Q478" s="2"/>
     </row>
-    <row r="479" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>12</v>
       </c>
@@ -26698,7 +27314,7 @@
       <c r="P479" s="2"/>
       <c r="Q479" s="2"/>
     </row>
-    <row r="480" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>12</v>
       </c>
@@ -26737,12 +27353,14 @@
       <c r="M480" s="2">
         <v>1</v>
       </c>
-      <c r="N480" s="2"/>
+      <c r="N480" s="10">
+        <v>46230</v>
+      </c>
       <c r="O480" s="2"/>
       <c r="P480" s="2"/>
       <c r="Q480" s="2"/>
     </row>
-    <row r="481" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>12</v>
       </c>
@@ -26786,7 +27404,7 @@
       <c r="P481" s="2"/>
       <c r="Q481" s="2"/>
     </row>
-    <row r="482" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>12</v>
       </c>
@@ -26800,7 +27418,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E482" s="2"/>
+      <c r="E482" s="2">
+        <v>21</v>
+      </c>
       <c r="F482" s="2" t="s">
         <v>963</v>
       </c>
@@ -26828,11 +27448,15 @@
       <c r="N482" s="10">
         <v>46227</v>
       </c>
-      <c r="O482" s="2"/>
-      <c r="P482" s="2"/>
+      <c r="O482" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P482" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q482" s="2"/>
     </row>
-    <row r="483" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>12</v>
       </c>
@@ -26846,7 +27470,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E483" s="2"/>
+      <c r="E483" s="2">
+        <v>21</v>
+      </c>
       <c r="F483" s="2" t="s">
         <v>1015</v>
       </c>
@@ -26874,11 +27500,15 @@
       <c r="N483" s="10">
         <v>46227</v>
       </c>
-      <c r="O483" s="2"/>
-      <c r="P483" s="2"/>
+      <c r="O483" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P483" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q483" s="2"/>
     </row>
-    <row r="484" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>12</v>
       </c>
@@ -26892,7 +27522,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E484" s="2"/>
+      <c r="E484" s="2">
+        <v>21</v>
+      </c>
       <c r="F484" s="2" t="s">
         <v>127</v>
       </c>
@@ -26920,8 +27552,12 @@
       <c r="N484" s="10">
         <v>46227</v>
       </c>
-      <c r="O484" s="2"/>
-      <c r="P484" s="2"/>
+      <c r="O484" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P484" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q484" s="2"/>
     </row>
     <row r="485" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -27028,7 +27664,7 @@
       </c>
       <c r="Q486" s="2"/>
     </row>
-    <row r="487" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>12</v>
       </c>
@@ -27042,7 +27678,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E487" s="2"/>
+      <c r="E487" s="2">
+        <v>21</v>
+      </c>
       <c r="F487" s="2" t="s">
         <v>127</v>
       </c>
@@ -27070,11 +27708,15 @@
       <c r="N487" s="10">
         <v>46227</v>
       </c>
-      <c r="O487" s="2"/>
-      <c r="P487" s="2"/>
+      <c r="O487" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P487" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q487" s="2"/>
     </row>
-    <row r="488" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>12</v>
       </c>
@@ -27118,7 +27760,7 @@
       <c r="P488" s="2"/>
       <c r="Q488" s="2"/>
     </row>
-    <row r="489" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>12</v>
       </c>
@@ -27214,7 +27856,7 @@
       </c>
       <c r="Q490" s="2"/>
     </row>
-    <row r="491" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>12</v>
       </c>
@@ -27228,7 +27870,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E491" s="2"/>
+      <c r="E491" s="2">
+        <v>21</v>
+      </c>
       <c r="F491" s="2" t="s">
         <v>127</v>
       </c>
@@ -27256,11 +27900,15 @@
       <c r="N491" s="10">
         <v>46227</v>
       </c>
-      <c r="O491" s="2"/>
-      <c r="P491" s="2"/>
+      <c r="O491" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P491" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q491" s="2"/>
     </row>
-    <row r="492" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>12</v>
       </c>
@@ -27274,7 +27922,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E492" s="2"/>
+      <c r="E492" s="2">
+        <v>21</v>
+      </c>
       <c r="F492" s="2" t="s">
         <v>127</v>
       </c>
@@ -27302,11 +27952,15 @@
       <c r="N492" s="10">
         <v>46227</v>
       </c>
-      <c r="O492" s="2"/>
-      <c r="P492" s="2"/>
+      <c r="O492" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P492" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q492" s="2"/>
     </row>
-    <row r="493" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>12</v>
       </c>
@@ -27320,7 +27974,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E493" s="2"/>
+      <c r="E493" s="2">
+        <v>21</v>
+      </c>
       <c r="F493" s="2" t="s">
         <v>13</v>
       </c>
@@ -27348,11 +28004,15 @@
       <c r="N493" s="10">
         <v>46227</v>
       </c>
-      <c r="O493" s="2"/>
-      <c r="P493" s="2"/>
+      <c r="O493" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P493" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q493" s="2"/>
     </row>
-    <row r="494" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>12</v>
       </c>
@@ -27366,7 +28026,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E494" s="2"/>
+      <c r="E494" s="2">
+        <v>21</v>
+      </c>
       <c r="F494" s="2" t="s">
         <v>13</v>
       </c>
@@ -27394,11 +28056,15 @@
       <c r="N494" s="10">
         <v>46227</v>
       </c>
-      <c r="O494" s="2"/>
-      <c r="P494" s="2"/>
+      <c r="O494" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P494" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q494" s="2"/>
     </row>
-    <row r="495" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>12</v>
       </c>
@@ -27442,7 +28108,7 @@
       <c r="P495" s="2"/>
       <c r="Q495" s="2"/>
     </row>
-    <row r="496" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>12</v>
       </c>
@@ -27486,7 +28152,7 @@
       <c r="P496" s="2"/>
       <c r="Q496" s="2"/>
     </row>
-    <row r="497" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>12</v>
       </c>
@@ -27530,7 +28196,7 @@
       <c r="P497" s="2"/>
       <c r="Q497" s="2"/>
     </row>
-    <row r="498" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>12</v>
       </c>
@@ -27544,7 +28210,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E498" s="2"/>
+      <c r="E498" s="2">
+        <v>21</v>
+      </c>
       <c r="F498" s="2" t="s">
         <v>13</v>
       </c>
@@ -27572,11 +28240,15 @@
       <c r="N498" s="10">
         <v>46227</v>
       </c>
-      <c r="O498" s="2"/>
-      <c r="P498" s="2"/>
+      <c r="O498" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P498" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q498" s="2"/>
     </row>
-    <row r="499" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>12</v>
       </c>
@@ -27620,7 +28292,7 @@
       <c r="P499" s="2"/>
       <c r="Q499" s="2"/>
     </row>
-    <row r="500" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>12</v>
       </c>
@@ -27634,7 +28306,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E500" s="2"/>
+      <c r="E500" s="2">
+        <v>21</v>
+      </c>
       <c r="F500" s="2" t="s">
         <v>13</v>
       </c>
@@ -27662,11 +28336,15 @@
       <c r="N500" s="10">
         <v>46227</v>
       </c>
-      <c r="O500" s="2"/>
-      <c r="P500" s="2"/>
+      <c r="O500" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P500" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q500" s="2"/>
     </row>
-    <row r="501" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>12</v>
       </c>
@@ -27710,7 +28388,7 @@
       <c r="P501" s="2"/>
       <c r="Q501" s="2"/>
     </row>
-    <row r="502" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>12</v>
       </c>
@@ -27754,7 +28432,7 @@
       <c r="P502" s="2"/>
       <c r="Q502" s="2"/>
     </row>
-    <row r="503" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>12</v>
       </c>
@@ -27793,12 +28471,14 @@
       <c r="M503" s="2">
         <v>1</v>
       </c>
-      <c r="N503" s="2"/>
+      <c r="N503" s="10">
+        <v>46230</v>
+      </c>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
       <c r="Q503" s="2"/>
     </row>
-    <row r="504" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>12</v>
       </c>
@@ -27842,7 +28522,7 @@
       <c r="P504" s="2"/>
       <c r="Q504" s="2"/>
     </row>
-    <row r="505" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>12</v>
       </c>
@@ -27886,7 +28566,7 @@
       <c r="P505" s="2"/>
       <c r="Q505" s="2"/>
     </row>
-    <row r="506" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>12</v>
       </c>
@@ -27900,7 +28580,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E506" s="2"/>
+      <c r="E506" s="2">
+        <v>21</v>
+      </c>
       <c r="F506" s="2" t="s">
         <v>13</v>
       </c>
@@ -27928,8 +28610,12 @@
       <c r="N506" s="10">
         <v>46227</v>
       </c>
-      <c r="O506" s="2"/>
-      <c r="P506" s="2"/>
+      <c r="O506" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P506" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q506" s="2"/>
     </row>
     <row r="507" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -28036,7 +28722,7 @@
       </c>
       <c r="Q508" s="2"/>
     </row>
-    <row r="509" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>12</v>
       </c>
@@ -28075,12 +28761,14 @@
       <c r="M509" s="2">
         <v>1</v>
       </c>
-      <c r="N509" s="2"/>
+      <c r="N509" s="10">
+        <v>46230</v>
+      </c>
       <c r="O509" s="2"/>
       <c r="P509" s="2"/>
       <c r="Q509" s="2"/>
     </row>
-    <row r="510" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>12</v>
       </c>
@@ -28094,7 +28782,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E510" s="2"/>
+      <c r="E510" s="2">
+        <v>21</v>
+      </c>
       <c r="F510" s="2" t="s">
         <v>13</v>
       </c>
@@ -28122,11 +28812,15 @@
       <c r="N510" s="10">
         <v>46227</v>
       </c>
-      <c r="O510" s="2"/>
-      <c r="P510" s="2"/>
+      <c r="O510" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P510" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q510" s="2"/>
     </row>
-    <row r="511" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>12</v>
       </c>
@@ -28140,7 +28834,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E511" s="2"/>
+      <c r="E511" s="2">
+        <v>21</v>
+      </c>
       <c r="F511" s="2" t="s">
         <v>13</v>
       </c>
@@ -28168,11 +28864,15 @@
       <c r="N511" s="10">
         <v>46227</v>
       </c>
-      <c r="O511" s="2"/>
-      <c r="P511" s="2"/>
+      <c r="O511" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P511" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q511" s="2"/>
     </row>
-    <row r="512" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>12</v>
       </c>
@@ -28216,7 +28916,7 @@
       <c r="P512" s="2"/>
       <c r="Q512" s="2"/>
     </row>
-    <row r="513" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>12</v>
       </c>
@@ -28230,7 +28930,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E513" s="2"/>
+      <c r="E513" s="2">
+        <v>21</v>
+      </c>
       <c r="F513" s="2" t="s">
         <v>13</v>
       </c>
@@ -28258,11 +28960,15 @@
       <c r="N513" s="10">
         <v>46227</v>
       </c>
-      <c r="O513" s="2"/>
-      <c r="P513" s="2"/>
+      <c r="O513" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P513" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q513" s="2"/>
     </row>
-    <row r="514" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>12</v>
       </c>
@@ -28276,7 +28982,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E514" s="2"/>
+      <c r="E514" s="2">
+        <v>21</v>
+      </c>
       <c r="F514" s="2" t="s">
         <v>529</v>
       </c>
@@ -28304,8 +29012,12 @@
       <c r="N514" s="10">
         <v>46227</v>
       </c>
-      <c r="O514" s="2"/>
-      <c r="P514" s="2"/>
+      <c r="O514" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P514" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q514" s="2"/>
     </row>
     <row r="515" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -28412,7 +29124,7 @@
       </c>
       <c r="Q516" s="2"/>
     </row>
-    <row r="517" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>12</v>
       </c>
@@ -28456,7 +29168,7 @@
       <c r="P517" s="2"/>
       <c r="Q517" s="2"/>
     </row>
-    <row r="518" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>12</v>
       </c>
@@ -28500,7 +29212,7 @@
       <c r="P518" s="2"/>
       <c r="Q518" s="2"/>
     </row>
-    <row r="519" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>12</v>
       </c>
@@ -28700,7 +29412,7 @@
       </c>
       <c r="Q522" s="2"/>
     </row>
-    <row r="523" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>12</v>
       </c>
@@ -28744,7 +29456,7 @@
       <c r="P523" s="2"/>
       <c r="Q523" s="2"/>
     </row>
-    <row r="524" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>12</v>
       </c>
@@ -28840,7 +29552,7 @@
       </c>
       <c r="Q525" s="2"/>
     </row>
-    <row r="526" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>12</v>
       </c>
@@ -28884,7 +29596,7 @@
       <c r="P526" s="2"/>
       <c r="Q526" s="2"/>
     </row>
-    <row r="527" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>12</v>
       </c>
@@ -28928,7 +29640,7 @@
       <c r="P527" s="2"/>
       <c r="Q527" s="2"/>
     </row>
-    <row r="528" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>12</v>
       </c>
@@ -28972,7 +29684,7 @@
       <c r="P528" s="2"/>
       <c r="Q528" s="2"/>
     </row>
-    <row r="529" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>12</v>
       </c>
@@ -28986,7 +29698,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E529" s="2"/>
+      <c r="E529" s="2">
+        <v>21</v>
+      </c>
       <c r="F529" s="2" t="s">
         <v>1020</v>
       </c>
@@ -29014,8 +29728,12 @@
       <c r="N529" s="10">
         <v>46227</v>
       </c>
-      <c r="O529" s="2"/>
-      <c r="P529" s="2"/>
+      <c r="O529" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P529" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q529" s="2"/>
     </row>
     <row r="530" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -29174,7 +29892,7 @@
       </c>
       <c r="Q532" s="2"/>
     </row>
-    <row r="533" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>12</v>
       </c>
@@ -29213,7 +29931,9 @@
       <c r="M533" s="2">
         <v>1</v>
       </c>
-      <c r="N533" s="2"/>
+      <c r="N533" s="10">
+        <v>46230</v>
+      </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
       <c r="Q533" s="2"/>
@@ -29270,7 +29990,7 @@
       </c>
       <c r="Q534" s="2"/>
     </row>
-    <row r="535" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>12</v>
       </c>
@@ -29366,7 +30086,7 @@
       </c>
       <c r="Q536" s="2"/>
     </row>
-    <row r="537" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>12</v>
       </c>
@@ -29514,7 +30234,7 @@
       </c>
       <c r="Q539" s="2"/>
     </row>
-    <row r="540" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>12</v>
       </c>
@@ -29558,23 +30278,25 @@
       <c r="P540" s="2"/>
       <c r="Q540" s="2"/>
     </row>
-    <row r="541" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1081</v>
+        <v>376</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1082</v>
+        <v>715</v>
       </c>
       <c r="D541" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E541" s="2"/>
+      <c r="E541" s="2">
+        <v>21</v>
+      </c>
       <c r="F541" s="2" t="s">
-        <v>1083</v>
+        <v>716</v>
       </c>
       <c r="G541" s="2" t="s">
         <v>24</v>
@@ -29583,23 +30305,29 @@
         <v>14</v>
       </c>
       <c r="I541" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J541" s="2">
         <v>1</v>
       </c>
       <c r="K541" s="11">
-        <v>4.2122000000000002</v>
+        <v>93.876760000000004</v>
       </c>
       <c r="L541" s="2">
-        <v>2.25</v>
+        <v>20</v>
       </c>
       <c r="M541" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="N541" s="2"/>
-      <c r="O541" s="2"/>
-      <c r="P541" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="N541" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O541" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P541" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q541" s="2"/>
     </row>
     <row r="542" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -29862,7 +30590,7 @@
       </c>
       <c r="Q546" s="2"/>
     </row>
-    <row r="547" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>12</v>
       </c>
@@ -29906,7 +30634,7 @@
       <c r="P547" s="2"/>
       <c r="Q547" s="2"/>
     </row>
-    <row r="548" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>12</v>
       </c>
@@ -29920,7 +30648,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E548" s="2"/>
+      <c r="E548" s="2">
+        <v>21</v>
+      </c>
       <c r="F548" s="2" t="s">
         <v>13</v>
       </c>
@@ -29948,8 +30678,12 @@
       <c r="N548" s="10">
         <v>46227</v>
       </c>
-      <c r="O548" s="2"/>
-      <c r="P548" s="2"/>
+      <c r="O548" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P548" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q548" s="2"/>
     </row>
     <row r="549" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -30004,7 +30738,7 @@
       </c>
       <c r="Q549" s="2"/>
     </row>
-    <row r="550" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>12</v>
       </c>
@@ -30048,7 +30782,7 @@
       <c r="P550" s="2"/>
       <c r="Q550" s="2"/>
     </row>
-    <row r="551" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>12</v>
       </c>
@@ -30092,7 +30826,7 @@
       <c r="P551" s="2"/>
       <c r="Q551" s="2"/>
     </row>
-    <row r="552" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>12</v>
       </c>
@@ -30131,12 +30865,14 @@
       <c r="M552" s="2">
         <v>1</v>
       </c>
-      <c r="N552" s="2"/>
+      <c r="N552" s="10">
+        <v>46230</v>
+      </c>
       <c r="O552" s="2"/>
       <c r="P552" s="2"/>
       <c r="Q552" s="2"/>
     </row>
-    <row r="553" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>12</v>
       </c>
@@ -30232,7 +30968,7 @@
       </c>
       <c r="Q554" s="2"/>
     </row>
-    <row r="555" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>12</v>
       </c>
@@ -30328,7 +31064,7 @@
       </c>
       <c r="Q556" s="2"/>
     </row>
-    <row r="557" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>12</v>
       </c>
@@ -30367,7 +31103,9 @@
       <c r="M557" s="2">
         <v>1</v>
       </c>
-      <c r="N557" s="2"/>
+      <c r="N557" s="10">
+        <v>46230</v>
+      </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
       <c r="Q557" s="2"/>
@@ -30424,7 +31162,7 @@
       </c>
       <c r="Q558" s="2"/>
     </row>
-    <row r="559" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>12</v>
       </c>
@@ -30520,7 +31258,7 @@
       </c>
       <c r="Q560" s="2"/>
     </row>
-    <row r="561" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>12</v>
       </c>
@@ -30616,7 +31354,7 @@
       </c>
       <c r="Q562" s="2"/>
     </row>
-    <row r="563" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>12</v>
       </c>
@@ -30972,7 +31710,7 @@
       </c>
       <c r="Q569" s="2"/>
     </row>
-    <row r="570" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>12</v>
       </c>
@@ -31120,23 +31858,25 @@
       </c>
       <c r="Q572" s="2"/>
     </row>
-    <row r="573" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1072</v>
+        <v>379</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1124</v>
+        <v>717</v>
       </c>
       <c r="D573" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E573" s="2"/>
+      <c r="E573" s="2">
+        <v>21</v>
+      </c>
       <c r="F573" s="2" t="s">
-        <v>1125</v>
+        <v>718</v>
       </c>
       <c r="G573" s="2" t="s">
         <v>24</v>
@@ -31151,20 +31891,26 @@
         <v>1</v>
       </c>
       <c r="K573" s="11">
-        <v>10.2316</v>
+        <v>88.287639999999996</v>
       </c>
       <c r="L573" s="2">
-        <v>6.75</v>
+        <v>18</v>
       </c>
       <c r="M573" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="N573" s="2"/>
-      <c r="O573" s="2"/>
-      <c r="P573" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="N573" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O573" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P573" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q573" s="2"/>
     </row>
-    <row r="574" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>12</v>
       </c>
@@ -31260,7 +32006,7 @@
       </c>
       <c r="Q575" s="2"/>
     </row>
-    <row r="576" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>12</v>
       </c>
@@ -31356,21 +32102,23 @@
       </c>
       <c r="Q577" s="2"/>
     </row>
-    <row r="578" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>345</v>
+        <v>543</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1132</v>
+        <v>770</v>
       </c>
       <c r="D578" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E578" s="2"/>
+      <c r="E578" s="2">
+        <v>21</v>
+      </c>
       <c r="F578" s="2" t="s">
         <v>13</v>
       </c>
@@ -31387,17 +32135,23 @@
         <v>1</v>
       </c>
       <c r="K578" s="11">
-        <v>16.493400000000001</v>
+        <v>5.0014000000000003</v>
       </c>
       <c r="L578" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M578" s="2">
         <v>2</v>
       </c>
-      <c r="N578" s="2"/>
-      <c r="O578" s="2"/>
-      <c r="P578" s="2"/>
+      <c r="N578" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O578" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P578" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q578" s="2"/>
     </row>
     <row r="579" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -31504,23 +32258,25 @@
       </c>
       <c r="Q580" s="2"/>
     </row>
-    <row r="581" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1136</v>
+        <v>345</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="D581" s="2" t="e">
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E581" s="2"/>
+      <c r="E581" s="2">
+        <v>21</v>
+      </c>
       <c r="F581" s="2" t="s">
-        <v>1138</v>
+        <v>13</v>
       </c>
       <c r="G581" s="2" t="s">
         <v>24</v>
@@ -31529,26 +32285,32 @@
         <v>14</v>
       </c>
       <c r="I581" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J581" s="2">
         <v>1</v>
       </c>
       <c r="K581" s="11">
-        <v>4.4652000000000003</v>
+        <v>16.493400000000001</v>
       </c>
       <c r="L581" s="2">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M581" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="N581" s="2"/>
-      <c r="O581" s="2"/>
-      <c r="P581" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="N581" s="10">
+        <v>46230</v>
+      </c>
+      <c r="O581" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P581" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q581" s="2"/>
     </row>
-    <row r="582" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>12</v>
       </c>
@@ -31562,7 +32324,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E582" s="2"/>
+      <c r="E582" s="2">
+        <v>21</v>
+      </c>
       <c r="F582" s="2" t="s">
         <v>13</v>
       </c>
@@ -31590,11 +32354,15 @@
       <c r="N582" s="10">
         <v>46227</v>
       </c>
-      <c r="O582" s="2"/>
-      <c r="P582" s="2"/>
+      <c r="O582" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P582" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q582" s="2"/>
     </row>
-    <row r="583" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>12</v>
       </c>
@@ -31638,7 +32406,7 @@
       <c r="P583" s="2"/>
       <c r="Q583" s="2"/>
     </row>
-    <row r="584" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>12</v>
       </c>
@@ -31734,7 +32502,7 @@
       </c>
       <c r="Q585" s="2"/>
     </row>
-    <row r="586" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>12</v>
       </c>
@@ -31778,7 +32546,7 @@
       <c r="P586" s="2"/>
       <c r="Q586" s="2"/>
     </row>
-    <row r="587" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>12</v>
       </c>
@@ -31822,7 +32590,7 @@
       <c r="P587" s="2"/>
       <c r="Q587" s="2"/>
     </row>
-    <row r="588" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>12</v>
       </c>
@@ -31866,7 +32634,7 @@
       <c r="P588" s="2"/>
       <c r="Q588" s="2"/>
     </row>
-    <row r="589" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>12</v>
       </c>
@@ -31910,7 +32678,7 @@
       <c r="P589" s="2"/>
       <c r="Q589" s="2"/>
     </row>
-    <row r="590" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>12</v>
       </c>
@@ -31954,7 +32722,7 @@
       <c r="P590" s="2"/>
       <c r="Q590" s="2"/>
     </row>
-    <row r="591" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>12</v>
       </c>
@@ -31968,7 +32736,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E591" s="2"/>
+      <c r="E591" s="2">
+        <v>21</v>
+      </c>
       <c r="F591" s="2" t="s">
         <v>13</v>
       </c>
@@ -31996,11 +32766,15 @@
       <c r="N591" s="10">
         <v>46227</v>
       </c>
-      <c r="O591" s="2"/>
-      <c r="P591" s="2"/>
+      <c r="O591" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P591" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q591" s="2"/>
     </row>
-    <row r="592" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>12</v>
       </c>
@@ -32096,7 +32870,7 @@
       </c>
       <c r="Q593" s="2"/>
     </row>
-    <row r="594" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>12</v>
       </c>
@@ -32192,7 +32966,7 @@
       </c>
       <c r="Q595" s="2"/>
     </row>
-    <row r="596" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>12</v>
       </c>
@@ -32236,7 +33010,7 @@
       <c r="P596" s="2"/>
       <c r="Q596" s="2"/>
     </row>
-    <row r="597" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>12</v>
       </c>
@@ -32280,7 +33054,7 @@
       <c r="P597" s="2"/>
       <c r="Q597" s="2"/>
     </row>
-    <row r="598" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>12</v>
       </c>
@@ -32376,7 +33150,7 @@
       </c>
       <c r="Q599" s="2"/>
     </row>
-    <row r="600" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>12</v>
       </c>
@@ -32524,7 +33298,7 @@
       </c>
       <c r="Q602" s="2"/>
     </row>
-    <row r="603" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>12</v>
       </c>
@@ -32620,7 +33394,7 @@
       </c>
       <c r="Q604" s="2"/>
     </row>
-    <row r="605" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>12</v>
       </c>
@@ -32664,7 +33438,7 @@
       <c r="P605" s="2"/>
       <c r="Q605" s="2"/>
     </row>
-    <row r="606" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>12</v>
       </c>
@@ -32708,7 +33482,7 @@
       <c r="P606" s="2"/>
       <c r="Q606" s="2"/>
     </row>
-    <row r="607" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>12</v>
       </c>
@@ -32752,7 +33526,7 @@
       <c r="P607" s="2"/>
       <c r="Q607" s="2"/>
     </row>
-    <row r="608" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>12</v>
       </c>
@@ -32766,7 +33540,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E608" s="2"/>
+      <c r="E608" s="2">
+        <v>21</v>
+      </c>
       <c r="F608" s="2" t="s">
         <v>127</v>
       </c>
@@ -32794,11 +33570,15 @@
       <c r="N608" s="10">
         <v>46227</v>
       </c>
-      <c r="O608" s="2"/>
-      <c r="P608" s="2"/>
+      <c r="O608" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P608" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q608" s="2"/>
     </row>
-    <row r="609" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>12</v>
       </c>
@@ -32812,7 +33592,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E609" s="2"/>
+      <c r="E609" s="2">
+        <v>21</v>
+      </c>
       <c r="F609" s="2" t="s">
         <v>127</v>
       </c>
@@ -32840,8 +33622,12 @@
       <c r="N609" s="10">
         <v>46227</v>
       </c>
-      <c r="O609" s="2"/>
-      <c r="P609" s="2"/>
+      <c r="O609" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P609" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q609" s="2"/>
     </row>
     <row r="610" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -32948,7 +33734,7 @@
       </c>
       <c r="Q611" s="2"/>
     </row>
-    <row r="612" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>12</v>
       </c>
@@ -32962,7 +33748,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E612" s="2"/>
+      <c r="E612" s="2">
+        <v>21</v>
+      </c>
       <c r="F612" s="2" t="s">
         <v>13</v>
       </c>
@@ -32990,11 +33778,15 @@
       <c r="N612" s="10">
         <v>46227</v>
       </c>
-      <c r="O612" s="2"/>
-      <c r="P612" s="2"/>
+      <c r="O612" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P612" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q612" s="2"/>
     </row>
-    <row r="613" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>12</v>
       </c>
@@ -33008,7 +33800,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E613" s="2"/>
+      <c r="E613" s="2">
+        <v>21</v>
+      </c>
       <c r="F613" s="2" t="s">
         <v>13</v>
       </c>
@@ -33036,8 +33830,12 @@
       <c r="N613" s="10">
         <v>46227</v>
       </c>
-      <c r="O613" s="2"/>
-      <c r="P613" s="2"/>
+      <c r="O613" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P613" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q613" s="2"/>
     </row>
     <row r="614" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -33092,7 +33890,7 @@
       </c>
       <c r="Q614" s="2"/>
     </row>
-    <row r="615" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>12</v>
       </c>
@@ -33106,7 +33904,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E615" s="2"/>
+      <c r="E615" s="2">
+        <v>21</v>
+      </c>
       <c r="F615" s="2" t="s">
         <v>13</v>
       </c>
@@ -33134,11 +33934,15 @@
       <c r="N615" s="10">
         <v>46227</v>
       </c>
-      <c r="O615" s="2"/>
-      <c r="P615" s="2"/>
+      <c r="O615" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P615" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q615" s="2"/>
     </row>
-    <row r="616" spans="1:17" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>12</v>
       </c>
@@ -33152,7 +33956,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="E616" s="2"/>
+      <c r="E616" s="2">
+        <v>21</v>
+      </c>
       <c r="F616" s="2" t="s">
         <v>13</v>
       </c>
@@ -33180,8 +33986,12 @@
       <c r="N616" s="10">
         <v>46227</v>
       </c>
-      <c r="O616" s="2"/>
-      <c r="P616" s="2"/>
+      <c r="O616" s="10">
+        <v>46230</v>
+      </c>
+      <c r="P616" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q616" s="2"/>
     </row>
     <row r="617" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -33437,10 +34247,10 @@
         <v>1193</v>
       </c>
       <c r="E5" s="12">
-        <v>162</v>
+        <v>281</v>
       </c>
       <c r="F5" s="12">
-        <v>4799</v>
+        <v>8076</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -33465,7 +34275,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED093DC9-3946-476F-9F4E-61288D40093D}">
-  <dimension ref="A1:A162"/>
+  <dimension ref="A1:A281"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -33769,7 +34579,7 @@
       <c r="A99" s="14"/>
     </row>
     <row r="100" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="15"/>
+      <c r="A100" s="16"/>
     </row>
     <row r="101" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="14"/>
@@ -33956,6 +34766,363 @@
     </row>
     <row r="162" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="15"/>
+    </row>
+    <row r="163" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="14"/>
+    </row>
+    <row r="164" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="15"/>
+    </row>
+    <row r="165" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="14"/>
+    </row>
+    <row r="166" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="15"/>
+    </row>
+    <row r="167" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="14"/>
+    </row>
+    <row r="168" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="15"/>
+    </row>
+    <row r="169" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="14"/>
+    </row>
+    <row r="170" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="15"/>
+    </row>
+    <row r="171" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="14"/>
+    </row>
+    <row r="172" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="15"/>
+    </row>
+    <row r="173" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="14"/>
+    </row>
+    <row r="174" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="15"/>
+    </row>
+    <row r="175" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="14"/>
+    </row>
+    <row r="176" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="15"/>
+    </row>
+    <row r="177" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="14"/>
+    </row>
+    <row r="178" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="15"/>
+    </row>
+    <row r="179" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="14"/>
+    </row>
+    <row r="180" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="15"/>
+    </row>
+    <row r="181" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="14"/>
+    </row>
+    <row r="182" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="15"/>
+    </row>
+    <row r="183" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="14"/>
+    </row>
+    <row r="184" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="15"/>
+    </row>
+    <row r="185" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="14"/>
+    </row>
+    <row r="186" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="15"/>
+    </row>
+    <row r="187" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="14"/>
+    </row>
+    <row r="188" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="15"/>
+    </row>
+    <row r="189" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="14"/>
+    </row>
+    <row r="190" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="15"/>
+    </row>
+    <row r="191" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="14"/>
+    </row>
+    <row r="192" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="15"/>
+    </row>
+    <row r="193" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="14"/>
+    </row>
+    <row r="194" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="15"/>
+    </row>
+    <row r="195" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="14"/>
+    </row>
+    <row r="196" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="15"/>
+    </row>
+    <row r="197" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="14"/>
+    </row>
+    <row r="198" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="15"/>
+    </row>
+    <row r="199" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="16"/>
+    </row>
+    <row r="200" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="15"/>
+    </row>
+    <row r="201" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="14"/>
+    </row>
+    <row r="202" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="15"/>
+    </row>
+    <row r="203" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="14"/>
+    </row>
+    <row r="204" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="15"/>
+    </row>
+    <row r="205" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="14"/>
+    </row>
+    <row r="206" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="15"/>
+    </row>
+    <row r="207" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="14"/>
+    </row>
+    <row r="208" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="15"/>
+    </row>
+    <row r="209" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="14"/>
+    </row>
+    <row r="210" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="15"/>
+    </row>
+    <row r="211" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="14"/>
+    </row>
+    <row r="212" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="15"/>
+    </row>
+    <row r="213" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="14"/>
+    </row>
+    <row r="214" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="15"/>
+    </row>
+    <row r="215" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="14"/>
+    </row>
+    <row r="216" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="15"/>
+    </row>
+    <row r="217" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="14"/>
+    </row>
+    <row r="218" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="15"/>
+    </row>
+    <row r="219" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="14"/>
+    </row>
+    <row r="220" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="15"/>
+    </row>
+    <row r="221" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="14"/>
+    </row>
+    <row r="222" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="15"/>
+    </row>
+    <row r="223" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="14"/>
+    </row>
+    <row r="224" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="15"/>
+    </row>
+    <row r="225" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="14"/>
+    </row>
+    <row r="226" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="15"/>
+    </row>
+    <row r="227" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="14"/>
+    </row>
+    <row r="228" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="15"/>
+    </row>
+    <row r="229" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="14"/>
+    </row>
+    <row r="230" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="15"/>
+    </row>
+    <row r="231" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="14"/>
+    </row>
+    <row r="232" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="15"/>
+    </row>
+    <row r="233" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="14"/>
+    </row>
+    <row r="234" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="15"/>
+    </row>
+    <row r="235" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="14"/>
+    </row>
+    <row r="236" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="15"/>
+    </row>
+    <row r="237" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="14"/>
+    </row>
+    <row r="238" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="15"/>
+    </row>
+    <row r="239" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="14"/>
+    </row>
+    <row r="240" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="15"/>
+    </row>
+    <row r="241" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="14"/>
+    </row>
+    <row r="242" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="15"/>
+    </row>
+    <row r="243" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="14"/>
+    </row>
+    <row r="244" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="15"/>
+    </row>
+    <row r="245" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="14"/>
+    </row>
+    <row r="246" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="15"/>
+    </row>
+    <row r="247" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="14"/>
+    </row>
+    <row r="248" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="15"/>
+    </row>
+    <row r="249" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="14"/>
+    </row>
+    <row r="250" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="15"/>
+    </row>
+    <row r="251" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="14"/>
+    </row>
+    <row r="252" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="15"/>
+    </row>
+    <row r="253" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="14"/>
+    </row>
+    <row r="254" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="15"/>
+    </row>
+    <row r="255" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="14"/>
+    </row>
+    <row r="256" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="15"/>
+    </row>
+    <row r="257" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="14"/>
+    </row>
+    <row r="258" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="15"/>
+    </row>
+    <row r="259" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="14"/>
+    </row>
+    <row r="260" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="15"/>
+    </row>
+    <row r="261" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="14"/>
+    </row>
+    <row r="262" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="15"/>
+    </row>
+    <row r="263" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="14"/>
+    </row>
+    <row r="264" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="15"/>
+    </row>
+    <row r="265" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="14"/>
+    </row>
+    <row r="266" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="15"/>
+    </row>
+    <row r="267" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="14"/>
+    </row>
+    <row r="268" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="15"/>
+    </row>
+    <row r="269" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="14"/>
+    </row>
+    <row r="270" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="15"/>
+    </row>
+    <row r="271" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="14"/>
+    </row>
+    <row r="272" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="15"/>
+    </row>
+    <row r="273" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="14"/>
+    </row>
+    <row r="274" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="15"/>
+    </row>
+    <row r="275" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="14"/>
+    </row>
+    <row r="276" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="15"/>
+    </row>
+    <row r="277" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="14"/>
+    </row>
+    <row r="278" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="15"/>
+    </row>
+    <row r="279" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="16"/>
+    </row>
+    <row r="280" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="15"/>
+    </row>
+    <row r="281" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/upload/packing/TJ-25-26-182 ( Small Bore ).xlsx
+++ b/data/upload/packing/TJ-25-26-182 ( Small Bore ).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\TJ-25-26-182 NE ( Vicksburg )\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7745785B-46EA-4E18-A9FA-9F4610F44CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8671C104-0F9F-40B1-9662-DB51CB2CBF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4631" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4647" uniqueCount="1198">
   <si>
     <t>Project Code</t>
   </si>
@@ -3639,7 +3639,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3685,6 +3685,12 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -3738,7 +3744,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -3815,12 +3821,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3858,9 +3875,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3869,6 +3883,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4634,7 +4654,7 @@
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.28515625" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.28515625" customWidth="1"/>
     <col min="7" max="7" width="14.7109375" customWidth="1"/>
@@ -4660,7 +4680,7 @@
       </c>
       <c r="K1" s="6">
         <f>SUBTOTAL(9,NavDataRegion[Total Wt])</f>
-        <v>16596.344509999995</v>
+        <v>16596.344509999992</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -11998,11 +12018,13 @@
       <c r="C157" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D157" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E157" s="2"/>
+      <c r="D157" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-LP-036-01</v>
+      </c>
+      <c r="E157" s="2">
+        <v>21</v>
+      </c>
       <c r="F157" s="2" t="s">
         <v>456</v>
       </c>
@@ -12027,9 +12049,15 @@
       <c r="M157" s="2">
         <v>0.75</v>
       </c>
-      <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
-      <c r="P157" s="2"/>
+      <c r="N157" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O157" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q157" s="2"/>
     </row>
     <row r="158" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13497,43 +13525,51 @@
         <v>12</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>537</v>
+        <v>63</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="D189" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E189" s="2"/>
+        <v>794</v>
+      </c>
+      <c r="D189" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-HP-017-03</v>
+      </c>
+      <c r="E189" s="2">
+        <v>21</v>
+      </c>
       <c r="F189" s="2" t="s">
-        <v>13</v>
+        <v>795</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J189" s="2">
         <v>1</v>
       </c>
       <c r="K189" s="11">
-        <v>4.4904000000000002</v>
+        <v>66.527479999999997</v>
       </c>
       <c r="L189" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M189" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
-      <c r="P189" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="N189" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O189" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P189" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q189" s="2"/>
     </row>
     <row r="190" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -13585,16 +13621,18 @@
         <v>12</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D191" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E191" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="D191" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-LP-079-01</v>
+      </c>
+      <c r="E191" s="2">
+        <v>21</v>
+      </c>
       <c r="F191" s="2" t="s">
         <v>13</v>
       </c>
@@ -13611,17 +13649,23 @@
         <v>1</v>
       </c>
       <c r="K191" s="11">
-        <v>8.9550000000000001</v>
+        <v>4.4904000000000002</v>
       </c>
       <c r="L191" s="2">
         <v>3</v>
       </c>
       <c r="M191" s="2">
-        <v>1</v>
-      </c>
-      <c r="N191" s="2"/>
-      <c r="O191" s="2"/>
-      <c r="P191" s="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="N191" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O191" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P191" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q191" s="2"/>
     </row>
     <row r="192" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -19780,13 +19824,15 @@
         <v>541</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="D322" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E322" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="D322" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-LP-081-01</v>
+      </c>
+      <c r="E322" s="2">
+        <v>21</v>
+      </c>
       <c r="F322" s="2" t="s">
         <v>13</v>
       </c>
@@ -19803,7 +19849,7 @@
         <v>1</v>
       </c>
       <c r="K322" s="11">
-        <v>8.48</v>
+        <v>8.9550000000000001</v>
       </c>
       <c r="L322" s="2">
         <v>3</v>
@@ -19811,9 +19857,15 @@
       <c r="M322" s="2">
         <v>1</v>
       </c>
-      <c r="N322" s="2"/>
-      <c r="O322" s="2"/>
-      <c r="P322" s="2"/>
+      <c r="N322" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O322" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P322" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q322" s="2"/>
     </row>
     <row r="323" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -20569,43 +20621,51 @@
         <v>12</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>63</v>
+        <v>541</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="D339" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E339" s="2"/>
+        <v>769</v>
+      </c>
+      <c r="D339" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-LP-081-02</v>
+      </c>
+      <c r="E339" s="2">
+        <v>21</v>
+      </c>
       <c r="F339" s="2" t="s">
-        <v>795</v>
+        <v>13</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H339" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I339" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J339" s="2">
         <v>1</v>
       </c>
       <c r="K339" s="11">
-        <v>66.527479999999997</v>
+        <v>8.48</v>
       </c>
       <c r="L339" s="2">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M339" s="2">
-        <v>2</v>
-      </c>
-      <c r="N339" s="2"/>
-      <c r="O339" s="2"/>
-      <c r="P339" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="N339" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O339" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P339" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q339" s="2"/>
     </row>
     <row r="340" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -23700,11 +23760,13 @@
       <c r="C404" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="D404" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E404" s="2"/>
+      <c r="D404" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-LP-081-03</v>
+      </c>
+      <c r="E404" s="2">
+        <v>21</v>
+      </c>
       <c r="F404" s="2" t="s">
         <v>13</v>
       </c>
@@ -23729,9 +23791,15 @@
       <c r="M404" s="2">
         <v>1</v>
       </c>
-      <c r="N404" s="2"/>
-      <c r="O404" s="2"/>
-      <c r="P404" s="2"/>
+      <c r="N404" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O404" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P404" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q404" s="2"/>
     </row>
     <row r="405" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -26628,11 +26696,13 @@
       <c r="C465" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="D465" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E465" s="2"/>
+      <c r="D465" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-LP-081-04</v>
+      </c>
+      <c r="E465" s="2">
+        <v>21</v>
+      </c>
       <c r="F465" s="2" t="s">
         <v>13</v>
       </c>
@@ -26657,9 +26727,15 @@
       <c r="M465" s="2">
         <v>1</v>
       </c>
-      <c r="N465" s="2"/>
-      <c r="O465" s="2"/>
-      <c r="P465" s="2"/>
+      <c r="N465" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O465" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P465" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q465" s="2"/>
     </row>
     <row r="466" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -28354,11 +28430,13 @@
       <c r="C501" s="2" t="s">
         <v>1023</v>
       </c>
-      <c r="D501" s="2" t="e">
-        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E501" s="2"/>
+      <c r="D501" s="2" t="str">
+        <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
+        <v>241537-1A-LP-081-05</v>
+      </c>
+      <c r="E501" s="2">
+        <v>21</v>
+      </c>
       <c r="F501" s="2" t="s">
         <v>13</v>
       </c>
@@ -28383,9 +28461,15 @@
       <c r="M501" s="2">
         <v>1</v>
       </c>
-      <c r="N501" s="2"/>
-      <c r="O501" s="2"/>
-      <c r="P501" s="2"/>
+      <c r="N501" s="10">
+        <v>46232</v>
+      </c>
+      <c r="O501" s="10">
+        <v>46232</v>
+      </c>
+      <c r="P501" s="2" t="s">
+        <v>1193</v>
+      </c>
       <c r="Q501" s="2"/>
     </row>
     <row r="502" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -34193,18 +34277,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:11" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>1187</v>
       </c>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
     </row>
     <row r="4" spans="2:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -34247,10 +34331,10 @@
         <v>1193</v>
       </c>
       <c r="E5" s="12">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F5" s="12">
-        <v>8076</v>
+        <v>8192</v>
       </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -34282,849 +34366,866 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14"/>
+      <c r="A1" s="16" t="s">
+        <v>794</v>
+      </c>
     </row>
     <row r="2" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
+      <c r="A2" s="16" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
+      <c r="A3" s="16" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="4" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
+      <c r="A4" s="16" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="5" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
+      <c r="A5" s="16" t="s">
+        <v>769</v>
+      </c>
     </row>
     <row r="6" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
+      <c r="A6" s="16" t="s">
+        <v>890</v>
+      </c>
     </row>
     <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
+      <c r="A7" s="16" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
+      <c r="A8" s="16" t="s">
+        <v>1023</v>
+      </c>
     </row>
     <row r="9" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
+      <c r="A9" s="13"/>
     </row>
     <row r="10" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
+      <c r="A10" s="14"/>
     </row>
     <row r="11" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
+      <c r="A11" s="13"/>
     </row>
     <row r="12" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
+      <c r="A12" s="14"/>
     </row>
     <row r="13" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
+      <c r="A13" s="13"/>
     </row>
     <row r="14" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
+      <c r="A14" s="14"/>
     </row>
     <row r="15" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
+      <c r="A15" s="13"/>
     </row>
     <row r="16" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
+      <c r="A16" s="14"/>
     </row>
     <row r="17" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
+      <c r="A17" s="13"/>
     </row>
     <row r="18" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
+      <c r="A18" s="14"/>
     </row>
     <row r="19" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
+      <c r="A19" s="13"/>
     </row>
     <row r="20" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
+      <c r="A20" s="14"/>
     </row>
     <row r="21" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
+      <c r="A21" s="13"/>
     </row>
     <row r="22" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
+      <c r="A22" s="14"/>
     </row>
     <row r="23" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
+      <c r="A23" s="13"/>
     </row>
     <row r="24" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
+      <c r="A24" s="14"/>
     </row>
     <row r="25" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
+      <c r="A25" s="13"/>
     </row>
     <row r="26" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
+      <c r="A26" s="14"/>
     </row>
     <row r="27" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
+      <c r="A27" s="13"/>
     </row>
     <row r="28" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
+      <c r="A28" s="14"/>
     </row>
     <row r="29" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
+      <c r="A29" s="13"/>
     </row>
     <row r="30" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
+      <c r="A30" s="14"/>
     </row>
     <row r="31" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
+      <c r="A31" s="13"/>
     </row>
     <row r="32" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="15"/>
+      <c r="A32" s="14"/>
     </row>
     <row r="33" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
+      <c r="A33" s="13"/>
     </row>
     <row r="34" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
+      <c r="A34" s="14"/>
     </row>
     <row r="35" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="14"/>
+      <c r="A35" s="13"/>
     </row>
     <row r="36" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
+      <c r="A36" s="14"/>
     </row>
     <row r="37" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="14"/>
+      <c r="A37" s="13"/>
     </row>
     <row r="38" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="15"/>
+      <c r="A38" s="14"/>
     </row>
     <row r="39" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14"/>
+      <c r="A39" s="13"/>
     </row>
     <row r="40" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="15"/>
+      <c r="A40" s="14"/>
     </row>
     <row r="41" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="14"/>
+      <c r="A41" s="13"/>
     </row>
     <row r="42" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="15"/>
+      <c r="A42" s="14"/>
     </row>
     <row r="43" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="14"/>
+      <c r="A43" s="13"/>
     </row>
     <row r="44" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="15"/>
+      <c r="A44" s="14"/>
     </row>
     <row r="45" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14"/>
+      <c r="A45" s="13"/>
     </row>
     <row r="46" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="15"/>
+      <c r="A46" s="14"/>
     </row>
     <row r="47" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="14"/>
+      <c r="A47" s="13"/>
     </row>
     <row r="48" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="15"/>
+      <c r="A48" s="14"/>
     </row>
     <row r="49" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="14"/>
+      <c r="A49" s="13"/>
     </row>
     <row r="50" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
+      <c r="A50" s="14"/>
     </row>
     <row r="51" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="14"/>
+      <c r="A51" s="13"/>
     </row>
     <row r="52" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="15"/>
+      <c r="A52" s="14"/>
     </row>
     <row r="53" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="14"/>
+      <c r="A53" s="13"/>
     </row>
     <row r="54" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="15"/>
+      <c r="A54" s="14"/>
     </row>
     <row r="55" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="14"/>
+      <c r="A55" s="13"/>
     </row>
     <row r="56" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15"/>
+      <c r="A56" s="14"/>
     </row>
     <row r="57" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="14"/>
+      <c r="A57" s="13"/>
     </row>
     <row r="58" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="15"/>
+      <c r="A58" s="14"/>
     </row>
     <row r="59" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="14"/>
+      <c r="A59" s="13"/>
     </row>
     <row r="60" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="15"/>
+      <c r="A60" s="14"/>
     </row>
     <row r="61" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="14"/>
+      <c r="A61" s="13"/>
     </row>
     <row r="62" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="15"/>
+      <c r="A62" s="14"/>
     </row>
     <row r="63" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="14"/>
+      <c r="A63" s="13"/>
     </row>
     <row r="64" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="15"/>
+      <c r="A64" s="14"/>
     </row>
     <row r="65" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="14"/>
+      <c r="A65" s="13"/>
     </row>
     <row r="66" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="15"/>
+      <c r="A66" s="14"/>
     </row>
     <row r="67" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="14"/>
+      <c r="A67" s="13"/>
     </row>
     <row r="68" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="15"/>
+      <c r="A68" s="14"/>
     </row>
     <row r="69" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="14"/>
+      <c r="A69" s="13"/>
     </row>
     <row r="70" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="15"/>
+      <c r="A70" s="14"/>
     </row>
     <row r="71" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="14"/>
+      <c r="A71" s="13"/>
     </row>
     <row r="72" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="15"/>
+      <c r="A72" s="14"/>
     </row>
     <row r="73" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="14"/>
+      <c r="A73" s="13"/>
     </row>
     <row r="74" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="15"/>
+      <c r="A74" s="14"/>
     </row>
     <row r="75" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="14"/>
+      <c r="A75" s="13"/>
     </row>
     <row r="76" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="15"/>
+      <c r="A76" s="14"/>
     </row>
     <row r="77" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="14"/>
+      <c r="A77" s="13"/>
     </row>
     <row r="78" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="15"/>
+      <c r="A78" s="14"/>
     </row>
     <row r="79" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="14"/>
+      <c r="A79" s="13"/>
     </row>
     <row r="80" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="15"/>
+      <c r="A80" s="14"/>
     </row>
     <row r="81" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="14"/>
+      <c r="A81" s="13"/>
     </row>
     <row r="82" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="15"/>
+      <c r="A82" s="14"/>
     </row>
     <row r="83" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="14"/>
+      <c r="A83" s="13"/>
     </row>
     <row r="84" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="15"/>
+      <c r="A84" s="14"/>
     </row>
     <row r="85" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="14"/>
+      <c r="A85" s="13"/>
     </row>
     <row r="86" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="15"/>
+      <c r="A86" s="14"/>
     </row>
     <row r="87" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="14"/>
+      <c r="A87" s="13"/>
     </row>
     <row r="88" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="15"/>
+      <c r="A88" s="14"/>
     </row>
     <row r="89" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="14"/>
+      <c r="A89" s="13"/>
     </row>
     <row r="90" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="15"/>
+      <c r="A90" s="14"/>
     </row>
     <row r="91" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="14"/>
+      <c r="A91" s="13"/>
     </row>
     <row r="92" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="15"/>
+      <c r="A92" s="14"/>
     </row>
     <row r="93" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="14"/>
+      <c r="A93" s="13"/>
     </row>
     <row r="94" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="15"/>
+      <c r="A94" s="14"/>
     </row>
     <row r="95" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="14"/>
+      <c r="A95" s="13"/>
     </row>
     <row r="96" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="15"/>
+      <c r="A96" s="14"/>
     </row>
     <row r="97" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="14"/>
+      <c r="A97" s="13"/>
     </row>
     <row r="98" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="15"/>
+      <c r="A98" s="14"/>
     </row>
     <row r="99" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="14"/>
+      <c r="A99" s="13"/>
     </row>
     <row r="100" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="16"/>
+      <c r="A100" s="15"/>
     </row>
     <row r="101" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="14"/>
+      <c r="A101" s="13"/>
     </row>
     <row r="102" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="15"/>
+      <c r="A102" s="14"/>
     </row>
     <row r="103" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="14"/>
+      <c r="A103" s="13"/>
     </row>
     <row r="104" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="15"/>
+      <c r="A104" s="14"/>
     </row>
     <row r="105" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="14"/>
+      <c r="A105" s="13"/>
     </row>
     <row r="106" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="15"/>
+      <c r="A106" s="14"/>
     </row>
     <row r="107" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="14"/>
+      <c r="A107" s="13"/>
     </row>
     <row r="108" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="15"/>
+      <c r="A108" s="14"/>
     </row>
     <row r="109" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="14"/>
+      <c r="A109" s="13"/>
     </row>
     <row r="110" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="15"/>
+      <c r="A110" s="14"/>
     </row>
     <row r="111" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="14"/>
+      <c r="A111" s="13"/>
     </row>
     <row r="112" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="15"/>
+      <c r="A112" s="14"/>
     </row>
     <row r="113" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="14"/>
+      <c r="A113" s="13"/>
     </row>
     <row r="114" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="15"/>
+      <c r="A114" s="14"/>
     </row>
     <row r="115" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="14"/>
+      <c r="A115" s="13"/>
     </row>
     <row r="116" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="15"/>
+      <c r="A116" s="14"/>
     </row>
     <row r="117" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="14"/>
+      <c r="A117" s="13"/>
     </row>
     <row r="118" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="15"/>
+      <c r="A118" s="14"/>
     </row>
     <row r="119" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="14"/>
+      <c r="A119" s="13"/>
     </row>
     <row r="120" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="15"/>
+      <c r="A120" s="14"/>
     </row>
     <row r="121" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="14"/>
+      <c r="A121" s="13"/>
     </row>
     <row r="122" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="15"/>
+      <c r="A122" s="14"/>
     </row>
     <row r="123" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="14"/>
+      <c r="A123" s="13"/>
     </row>
     <row r="124" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="15"/>
+      <c r="A124" s="14"/>
     </row>
     <row r="125" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="14"/>
+      <c r="A125" s="13"/>
     </row>
     <row r="126" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="15"/>
+      <c r="A126" s="14"/>
     </row>
     <row r="127" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="14"/>
+      <c r="A127" s="13"/>
     </row>
     <row r="128" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="15"/>
+      <c r="A128" s="14"/>
     </row>
     <row r="129" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="14"/>
+      <c r="A129" s="13"/>
     </row>
     <row r="130" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="15"/>
+      <c r="A130" s="14"/>
     </row>
     <row r="131" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="14"/>
+      <c r="A131" s="13"/>
     </row>
     <row r="132" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="15"/>
+      <c r="A132" s="14"/>
     </row>
     <row r="133" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="14"/>
+      <c r="A133" s="13"/>
     </row>
     <row r="134" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="15"/>
+      <c r="A134" s="14"/>
     </row>
     <row r="135" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="14"/>
+      <c r="A135" s="13"/>
     </row>
     <row r="136" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="15"/>
+      <c r="A136" s="14"/>
     </row>
     <row r="137" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="14"/>
+      <c r="A137" s="13"/>
     </row>
     <row r="138" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="15"/>
+      <c r="A138" s="14"/>
     </row>
     <row r="139" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="14"/>
+      <c r="A139" s="13"/>
     </row>
     <row r="140" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="15"/>
+      <c r="A140" s="14"/>
     </row>
     <row r="141" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="14"/>
+      <c r="A141" s="13"/>
     </row>
     <row r="142" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="15"/>
+      <c r="A142" s="14"/>
     </row>
     <row r="143" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="14"/>
+      <c r="A143" s="13"/>
     </row>
     <row r="144" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="15"/>
+      <c r="A144" s="14"/>
     </row>
     <row r="145" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="14"/>
+      <c r="A145" s="13"/>
     </row>
     <row r="146" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="15"/>
+      <c r="A146" s="14"/>
     </row>
     <row r="147" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="14"/>
+      <c r="A147" s="13"/>
     </row>
     <row r="148" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="15"/>
+      <c r="A148" s="14"/>
     </row>
     <row r="149" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="14"/>
+      <c r="A149" s="13"/>
     </row>
     <row r="150" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="15"/>
+      <c r="A150" s="14"/>
     </row>
     <row r="151" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="14"/>
+      <c r="A151" s="13"/>
     </row>
     <row r="152" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="15"/>
+      <c r="A152" s="14"/>
     </row>
     <row r="153" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="14"/>
+      <c r="A153" s="13"/>
     </row>
     <row r="154" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="15"/>
+      <c r="A154" s="14"/>
     </row>
     <row r="155" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="14"/>
+      <c r="A155" s="13"/>
     </row>
     <row r="156" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="15"/>
+      <c r="A156" s="14"/>
     </row>
     <row r="157" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="14"/>
+      <c r="A157" s="13"/>
     </row>
     <row r="158" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="15"/>
+      <c r="A158" s="14"/>
     </row>
     <row r="159" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="14"/>
+      <c r="A159" s="13"/>
     </row>
     <row r="160" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="15"/>
+      <c r="A160" s="14"/>
     </row>
     <row r="161" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="14"/>
+      <c r="A161" s="13"/>
     </row>
     <row r="162" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="15"/>
+      <c r="A162" s="14"/>
     </row>
     <row r="163" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="14"/>
+      <c r="A163" s="13"/>
     </row>
     <row r="164" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="15"/>
+      <c r="A164" s="14"/>
     </row>
     <row r="165" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="14"/>
+      <c r="A165" s="13"/>
     </row>
     <row r="166" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="15"/>
+      <c r="A166" s="14"/>
     </row>
     <row r="167" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="14"/>
+      <c r="A167" s="13"/>
     </row>
     <row r="168" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="15"/>
+      <c r="A168" s="14"/>
     </row>
     <row r="169" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="14"/>
+      <c r="A169" s="13"/>
     </row>
     <row r="170" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="15"/>
+      <c r="A170" s="14"/>
     </row>
     <row r="171" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="14"/>
+      <c r="A171" s="13"/>
     </row>
     <row r="172" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="15"/>
+      <c r="A172" s="14"/>
     </row>
     <row r="173" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="14"/>
+      <c r="A173" s="13"/>
     </row>
     <row r="174" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="15"/>
+      <c r="A174" s="14"/>
     </row>
     <row r="175" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="14"/>
+      <c r="A175" s="13"/>
     </row>
     <row r="176" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="15"/>
+      <c r="A176" s="14"/>
     </row>
     <row r="177" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="14"/>
+      <c r="A177" s="13"/>
     </row>
     <row r="178" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="15"/>
+      <c r="A178" s="14"/>
     </row>
     <row r="179" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="14"/>
+      <c r="A179" s="13"/>
     </row>
     <row r="180" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="15"/>
+      <c r="A180" s="14"/>
     </row>
     <row r="181" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="14"/>
+      <c r="A181" s="13"/>
     </row>
     <row r="182" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="15"/>
+      <c r="A182" s="14"/>
     </row>
     <row r="183" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="14"/>
+      <c r="A183" s="13"/>
     </row>
     <row r="184" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="15"/>
+      <c r="A184" s="14"/>
     </row>
     <row r="185" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="14"/>
+      <c r="A185" s="13"/>
     </row>
     <row r="186" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="15"/>
+      <c r="A186" s="14"/>
     </row>
     <row r="187" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="14"/>
+      <c r="A187" s="13"/>
     </row>
     <row r="188" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="15"/>
+      <c r="A188" s="14"/>
     </row>
     <row r="189" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="14"/>
+      <c r="A189" s="13"/>
     </row>
     <row r="190" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="15"/>
+      <c r="A190" s="14"/>
     </row>
     <row r="191" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="14"/>
+      <c r="A191" s="13"/>
     </row>
     <row r="192" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="15"/>
+      <c r="A192" s="14"/>
     </row>
     <row r="193" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="14"/>
+      <c r="A193" s="13"/>
     </row>
     <row r="194" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="15"/>
+      <c r="A194" s="14"/>
     </row>
     <row r="195" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="14"/>
+      <c r="A195" s="13"/>
     </row>
     <row r="196" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="15"/>
+      <c r="A196" s="14"/>
     </row>
     <row r="197" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="14"/>
+      <c r="A197" s="13"/>
     </row>
     <row r="198" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="15"/>
+      <c r="A198" s="14"/>
     </row>
     <row r="199" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="16"/>
+      <c r="A199" s="15"/>
     </row>
     <row r="200" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="15"/>
+      <c r="A200" s="14"/>
     </row>
     <row r="201" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="14"/>
+      <c r="A201" s="13"/>
     </row>
     <row r="202" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="15"/>
+      <c r="A202" s="14"/>
     </row>
     <row r="203" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="14"/>
+      <c r="A203" s="13"/>
     </row>
     <row r="204" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="15"/>
+      <c r="A204" s="14"/>
     </row>
     <row r="205" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="14"/>
+      <c r="A205" s="13"/>
     </row>
     <row r="206" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="15"/>
+      <c r="A206" s="14"/>
     </row>
     <row r="207" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="14"/>
+      <c r="A207" s="13"/>
     </row>
     <row r="208" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="15"/>
+      <c r="A208" s="14"/>
     </row>
     <row r="209" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="14"/>
+      <c r="A209" s="13"/>
     </row>
     <row r="210" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="15"/>
+      <c r="A210" s="14"/>
     </row>
     <row r="211" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="14"/>
+      <c r="A211" s="13"/>
     </row>
     <row r="212" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="15"/>
+      <c r="A212" s="14"/>
     </row>
     <row r="213" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="14"/>
+      <c r="A213" s="13"/>
     </row>
     <row r="214" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="15"/>
+      <c r="A214" s="14"/>
     </row>
     <row r="215" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="14"/>
+      <c r="A215" s="13"/>
     </row>
     <row r="216" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="15"/>
+      <c r="A216" s="14"/>
     </row>
     <row r="217" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="14"/>
+      <c r="A217" s="13"/>
     </row>
     <row r="218" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="15"/>
+      <c r="A218" s="14"/>
     </row>
     <row r="219" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="14"/>
+      <c r="A219" s="13"/>
     </row>
     <row r="220" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="15"/>
+      <c r="A220" s="14"/>
     </row>
     <row r="221" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="14"/>
+      <c r="A221" s="13"/>
     </row>
     <row r="222" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="15"/>
+      <c r="A222" s="14"/>
     </row>
     <row r="223" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="14"/>
+      <c r="A223" s="13"/>
     </row>
     <row r="224" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="15"/>
+      <c r="A224" s="14"/>
     </row>
     <row r="225" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="14"/>
+      <c r="A225" s="13"/>
     </row>
     <row r="226" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="15"/>
+      <c r="A226" s="14"/>
     </row>
     <row r="227" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="14"/>
+      <c r="A227" s="13"/>
     </row>
     <row r="228" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="15"/>
+      <c r="A228" s="14"/>
     </row>
     <row r="229" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="14"/>
+      <c r="A229" s="13"/>
     </row>
     <row r="230" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="15"/>
+      <c r="A230" s="14"/>
     </row>
     <row r="231" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="14"/>
+      <c r="A231" s="13"/>
     </row>
     <row r="232" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="15"/>
+      <c r="A232" s="14"/>
     </row>
     <row r="233" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="14"/>
+      <c r="A233" s="13"/>
     </row>
     <row r="234" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="15"/>
+      <c r="A234" s="14"/>
     </row>
     <row r="235" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="14"/>
+      <c r="A235" s="13"/>
     </row>
     <row r="236" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="15"/>
+      <c r="A236" s="14"/>
     </row>
     <row r="237" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="14"/>
+      <c r="A237" s="13"/>
     </row>
     <row r="238" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="15"/>
+      <c r="A238" s="14"/>
     </row>
     <row r="239" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="14"/>
+      <c r="A239" s="13"/>
     </row>
     <row r="240" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="15"/>
+      <c r="A240" s="14"/>
     </row>
     <row r="241" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="14"/>
+      <c r="A241" s="13"/>
     </row>
     <row r="242" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="15"/>
+      <c r="A242" s="14"/>
     </row>
     <row r="243" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="14"/>
+      <c r="A243" s="13"/>
     </row>
     <row r="244" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="15"/>
+      <c r="A244" s="14"/>
     </row>
     <row r="245" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="14"/>
+      <c r="A245" s="13"/>
     </row>
     <row r="246" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="15"/>
+      <c r="A246" s="14"/>
     </row>
     <row r="247" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="14"/>
+      <c r="A247" s="13"/>
     </row>
     <row r="248" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="15"/>
+      <c r="A248" s="14"/>
     </row>
     <row r="249" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="14"/>
+      <c r="A249" s="13"/>
     </row>
     <row r="250" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="15"/>
+      <c r="A250" s="14"/>
     </row>
     <row r="251" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="14"/>
+      <c r="A251" s="13"/>
     </row>
     <row r="252" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="15"/>
+      <c r="A252" s="14"/>
     </row>
     <row r="253" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="14"/>
+      <c r="A253" s="13"/>
     </row>
     <row r="254" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="15"/>
+      <c r="A254" s="14"/>
     </row>
     <row r="255" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="14"/>
+      <c r="A255" s="13"/>
     </row>
     <row r="256" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="15"/>
+      <c r="A256" s="14"/>
     </row>
     <row r="257" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="14"/>
+      <c r="A257" s="13"/>
     </row>
     <row r="258" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="15"/>
+      <c r="A258" s="14"/>
     </row>
     <row r="259" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="14"/>
+      <c r="A259" s="13"/>
     </row>
     <row r="260" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="15"/>
+      <c r="A260" s="14"/>
     </row>
     <row r="261" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="14"/>
+      <c r="A261" s="13"/>
     </row>
     <row r="262" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="15"/>
+      <c r="A262" s="14"/>
     </row>
     <row r="263" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="14"/>
+      <c r="A263" s="13"/>
     </row>
     <row r="264" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="15"/>
+      <c r="A264" s="14"/>
     </row>
     <row r="265" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="14"/>
+      <c r="A265" s="13"/>
     </row>
     <row r="266" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="15"/>
+      <c r="A266" s="14"/>
     </row>
     <row r="267" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="14"/>
+      <c r="A267" s="13"/>
     </row>
     <row r="268" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="15"/>
+      <c r="A268" s="14"/>
     </row>
     <row r="269" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="14"/>
+      <c r="A269" s="13"/>
     </row>
     <row r="270" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="15"/>
+      <c r="A270" s="14"/>
     </row>
     <row r="271" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="14"/>
+      <c r="A271" s="13"/>
     </row>
     <row r="272" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="15"/>
+      <c r="A272" s="14"/>
     </row>
     <row r="273" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="14"/>
+      <c r="A273" s="13"/>
     </row>
     <row r="274" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="15"/>
+      <c r="A274" s="14"/>
     </row>
     <row r="275" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="14"/>
+      <c r="A275" s="13"/>
     </row>
     <row r="276" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="15"/>
+      <c r="A276" s="14"/>
     </row>
     <row r="277" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="14"/>
+      <c r="A277" s="13"/>
     </row>
     <row r="278" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="15"/>
+      <c r="A278" s="14"/>
     </row>
     <row r="279" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="16"/>
+      <c r="A279" s="15"/>
     </row>
     <row r="280" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="15"/>
+      <c r="A280" s="14"/>
     </row>
     <row r="281" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="14"/>
+      <c r="A281" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>